--- a/data/Rossall/CL32-RO-May.xlsx
+++ b/data/Rossall/CL32-RO-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Rossall\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECF063A-4FED-4322-9651-3F8C11077A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B40BC5-3FFD-4C20-8519-7680438E26D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{330082E0-B90D-417B-B816-56D44A1F8E8F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$570</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$544</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3143" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3030" uniqueCount="951">
   <si>
     <t>Activity ID</t>
   </si>
@@ -1922,12 +1922,6 @@
     <t>Trial Holes &amp; Route Proving</t>
   </si>
   <si>
-    <t>23.66d</t>
-  </si>
-  <si>
-    <t>73.34d</t>
-  </si>
-  <si>
     <t xml:space="preserve">        AMP8-DD&amp;B-ROS-CON-6400</t>
   </si>
   <si>
@@ -1940,24 +1934,12 @@
     <t>Cable up cabins</t>
   </si>
   <si>
-    <t xml:space="preserve">    Fleetwood - Construction Programme - 28.01.26 5 Day Working 24Hr Tunnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Milestones</t>
-  </si>
-  <si>
     <t xml:space="preserve">        AMP8-DD&amp;B-ROS-MIL-2520</t>
   </si>
   <si>
     <t>Project Start</t>
   </si>
   <si>
-    <t xml:space="preserve">      Compounds</t>
-  </si>
-  <si>
-    <t>17.00d</t>
-  </si>
-  <si>
     <t>61.00d</t>
   </si>
   <si>
@@ -1988,9 +1970,6 @@
     <t>06-Apr-26 A</t>
   </si>
   <si>
-    <t xml:space="preserve">        Shaft 7 Compound</t>
-  </si>
-  <si>
     <t xml:space="preserve">          AMP8-DD&amp;B-ROS-CON-1070</t>
   </si>
   <si>
@@ -2015,9 +1994,6 @@
     <t>Create Bellmouth Entrance</t>
   </si>
   <si>
-    <t xml:space="preserve">        Shaft 5 Compound</t>
-  </si>
-  <si>
     <t xml:space="preserve">          AMP8-DD&amp;B-ROS-CON-1110</t>
   </si>
   <si>
@@ -2042,9 +2018,6 @@
     <t xml:space="preserve">          AMP8-DD&amp;B-ROS-CON-6020</t>
   </si>
   <si>
-    <t xml:space="preserve">        Shafts 3 &amp; 4 (Access During School Half Term)</t>
-  </si>
-  <si>
     <t xml:space="preserve">          AMP8-DD&amp;B-ROS-CON-2600</t>
   </si>
   <si>
@@ -2105,9 +2078,6 @@
     <t>Install Dropped Kerb &amp; Access</t>
   </si>
   <si>
-    <t xml:space="preserve">        Shaft 2 Compound</t>
-  </si>
-  <si>
     <t xml:space="preserve">          AMP8-DD&amp;B-ROS-CON-1720</t>
   </si>
   <si>
@@ -2186,12 +2156,6 @@
     <t>Create piling Platform - 25m x 25m</t>
   </si>
   <si>
-    <t xml:space="preserve">        Shaft 1 Compound</t>
-  </si>
-  <si>
-    <t>52.00d</t>
-  </si>
-  <si>
     <t xml:space="preserve">          AMP8-DD&amp;B-ROS-CON-1090</t>
   </si>
   <si>
@@ -2246,9 +2210,6 @@
     <t>17.54d</t>
   </si>
   <si>
-    <t xml:space="preserve">            Cutting Edge &amp; Jacking collar</t>
-  </si>
-  <si>
     <t xml:space="preserve">              AMP8-DD&amp;B-ROS-CON-1000</t>
   </si>
   <si>
@@ -2327,12 +2288,6 @@
     <t>Concrete - Collar - 000m3</t>
   </si>
   <si>
-    <t xml:space="preserve">            Shaft Sinking (muck, Build, Wrap)</t>
-  </si>
-  <si>
-    <t>12.50d</t>
-  </si>
-  <si>
     <t>11.50d</t>
   </si>
   <si>
@@ -2372,9 +2327,6 @@
     <t>Ring no 23 ( ≈1 ring /1.5d)</t>
   </si>
   <si>
-    <t xml:space="preserve">            Plug &amp; Grouting</t>
-  </si>
-  <si>
     <t>10.00d</t>
   </si>
   <si>
@@ -2414,18 +2366,12 @@
     <t>Grout Annulus</t>
   </si>
   <si>
-    <t xml:space="preserve">            Structure Base</t>
-  </si>
-  <si>
     <t xml:space="preserve">              AMP8-DD&amp;B-ROS-CON-5840</t>
   </si>
   <si>
     <t>Steel Fixing - ≈18.5 ton</t>
   </si>
   <si>
-    <t xml:space="preserve">          Shaft 5 West Way</t>
-  </si>
-  <si>
     <t xml:space="preserve">              AMP8-DD&amp;B-ROS-CON-5860</t>
   </si>
   <si>
@@ -2465,9 +2411,6 @@
     <t>Concrete - Collar</t>
   </si>
   <si>
-    <t>9.50d</t>
-  </si>
-  <si>
     <t xml:space="preserve">              AMP8-DD&amp;B-ROS-CON-5940</t>
   </si>
   <si>
@@ -2549,15 +2492,9 @@
     <t>18.52d</t>
   </si>
   <si>
-    <t xml:space="preserve">          Shaft 3  Cardinal Allen High School</t>
-  </si>
-  <si>
     <t>19.00d</t>
   </si>
   <si>
-    <t>19.97d</t>
-  </si>
-  <si>
     <t xml:space="preserve">            Guide Wall</t>
   </si>
   <si>
@@ -2612,9 +2549,6 @@
     <t>05-Apr-26 A</t>
   </si>
   <si>
-    <t>21.20d</t>
-  </si>
-  <si>
     <t>26.30d</t>
   </si>
   <si>
@@ -2660,15 +2594,6 @@
     <t>Piling work- 9 hard pile (1 pile/d, pile depth ≈ 22m</t>
   </si>
   <si>
-    <t xml:space="preserve">            Shaft Excavatin</t>
-  </si>
-  <si>
-    <t>4.80d</t>
-  </si>
-  <si>
-    <t>18.97d</t>
-  </si>
-  <si>
     <t xml:space="preserve">              AMP8-DD&amp;B-ROS-CON-6070</t>
   </si>
   <si>
@@ -2696,12 +2621,6 @@
     <t xml:space="preserve">              AMP8-DD&amp;B-ROS-CON-5720</t>
   </si>
   <si>
-    <t xml:space="preserve">          Shaft 4  Cardinal Allen High School</t>
-  </si>
-  <si>
-    <t>34.98d</t>
-  </si>
-  <si>
     <t>25.52d</t>
   </si>
   <si>
@@ -2739,9 +2658,6 @@
   </si>
   <si>
     <t xml:space="preserve">              AMP8-DD&amp;B-ROS-CON-6730</t>
-  </si>
-  <si>
-    <t>28.98d</t>
   </si>
   <si>
     <t xml:space="preserve">              AMP8-DD&amp;B-ROS-CON-6600</t>
@@ -2991,7 +2907,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3007,12 +2923,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3053,7 +2963,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3084,27 +2994,20 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3441,10 +3344,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884A9926-2854-412E-98E6-E3B0E258D9F8}">
-  <dimension ref="A1:G570"/>
+  <dimension ref="A1:G544"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.85546875" customWidth="1"/>
+    <col min="1" max="1" width="45.85546875" customWidth="1"/>
     <col min="2" max="2" width="71.28515625" customWidth="1"/>
     <col min="3" max="4" width="14.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
@@ -3510,21 +3413,21 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14" t="s">
+      <c r="E4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3569,21 +3472,21 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="12"/>
+      <c r="C7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="E7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -3626,21 +3529,21 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15" t="s">
+      <c r="B10" s="12"/>
+      <c r="C10" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
+      <c r="E10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -3683,21 +3586,21 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="E13" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -3720,21 +3623,21 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="15" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
+      <c r="E15" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -3777,21 +3680,21 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="12"/>
+      <c r="C18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
+      <c r="E18" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -3834,21 +3737,21 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="15" t="s">
+      <c r="B21" s="12"/>
+      <c r="C21" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="E21" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -3891,21 +3794,21 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="15" t="s">
+      <c r="B24" s="12"/>
+      <c r="C24" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="E24" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -3948,38 +3851,38 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13" t="s">
+      <c r="B27" s="10"/>
+      <c r="C27" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
+      <c r="E27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="15" t="s">
+      <c r="B28" s="12"/>
+      <c r="C28" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
+      <c r="E28" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -4022,21 +3925,21 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15" t="s">
+      <c r="B31" s="12"/>
+      <c r="C31" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
+      <c r="E31" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -4079,21 +3982,21 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15" t="s">
+      <c r="B34" s="12"/>
+      <c r="C34" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E34" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14" t="s">
+      <c r="E34" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4138,21 +4041,21 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="12"/>
+      <c r="C37" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14" t="s">
+      <c r="E37" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4197,21 +4100,21 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="15" t="s">
+      <c r="B40" s="12"/>
+      <c r="C40" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14" t="s">
+      <c r="E40" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4256,21 +4159,21 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="15" t="s">
+      <c r="B43" s="12"/>
+      <c r="C43" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E43" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+      <c r="E43" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -4350,21 +4253,21 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="15" t="s">
+      <c r="B48" s="12"/>
+      <c r="C48" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
+      <c r="E48" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -4427,21 +4330,21 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="15" t="s">
+      <c r="B52" s="12"/>
+      <c r="C52" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D52" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E52" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
+      <c r="E52" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -4504,21 +4407,21 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="15" t="s">
+      <c r="B56" s="12"/>
+      <c r="C56" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E56" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
+      <c r="E56" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -4581,21 +4484,21 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="15" t="s">
+      <c r="B60" s="12"/>
+      <c r="C60" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D60" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E60" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
+      <c r="E60" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -4658,21 +4561,21 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="15" t="s">
+      <c r="B64" s="12"/>
+      <c r="C64" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="D64" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="E64" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
+      <c r="E64" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
@@ -4735,21 +4638,21 @@
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="15" t="s">
+      <c r="B68" s="12"/>
+      <c r="C68" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E68" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
+      <c r="E68" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -4812,21 +4715,21 @@
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13" t="s">
+      <c r="B72" s="10"/>
+      <c r="C72" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="E72" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
+      <c r="E72" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="10"/>
+      <c r="G72" s="10"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -4849,21 +4752,21 @@
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="15" t="s">
+      <c r="B74" s="12"/>
+      <c r="C74" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E74" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
+      <c r="E74" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -4943,21 +4846,21 @@
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B79" s="14"/>
-      <c r="C79" s="15" t="s">
+      <c r="B79" s="12"/>
+      <c r="C79" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E79" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
+      <c r="E79" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
@@ -5037,21 +4940,21 @@
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B84" s="14"/>
-      <c r="C84" s="15" t="s">
+      <c r="B84" s="12"/>
+      <c r="C84" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="D84" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E84" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
+      <c r="E84" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
@@ -5114,21 +5017,21 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B88" s="14"/>
-      <c r="C88" s="15" t="s">
+      <c r="B88" s="12"/>
+      <c r="C88" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D88" s="15" t="s">
+      <c r="D88" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E88" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
+      <c r="E88" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
@@ -5211,38 +5114,38 @@
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="12" t="s">
+      <c r="A93" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B93" s="12"/>
-      <c r="C93" s="13" t="s">
+      <c r="B93" s="10"/>
+      <c r="C93" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D93" s="13" t="s">
+      <c r="D93" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E93" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" s="12"/>
-      <c r="G93" s="12"/>
+      <c r="E93" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="10"/>
+      <c r="G93" s="10"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B94" s="14"/>
-      <c r="C94" s="15" t="s">
+      <c r="B94" s="12"/>
+      <c r="C94" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D94" s="15" t="s">
+      <c r="D94" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E94" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
+      <c r="E94" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -5322,38 +5225,38 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B99" s="10"/>
-      <c r="C99" s="11" t="s">
+      <c r="B99" s="8"/>
+      <c r="C99" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D99" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E99" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" s="10"/>
-      <c r="G99" s="10"/>
+      <c r="E99" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="12" t="s">
+      <c r="A100" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B100" s="12"/>
-      <c r="C100" s="13" t="s">
+      <c r="B100" s="10"/>
+      <c r="C100" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D100" s="13" t="s">
+      <c r="D100" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E100" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="12"/>
-      <c r="G100" s="12"/>
+      <c r="E100" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="10"/>
+      <c r="G100" s="10"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
@@ -5393,21 +5296,21 @@
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="12" t="s">
+      <c r="A103" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B103" s="12"/>
-      <c r="C103" s="13" t="s">
+      <c r="B103" s="10"/>
+      <c r="C103" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D103" s="13" t="s">
+      <c r="D103" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E103" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F103" s="12"/>
-      <c r="G103" s="12"/>
+      <c r="E103" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" s="10"/>
+      <c r="G103" s="10"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
@@ -5447,21 +5350,21 @@
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B106" s="12"/>
-      <c r="C106" s="13" t="s">
+      <c r="B106" s="10"/>
+      <c r="C106" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D106" s="13" t="s">
+      <c r="D106" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E106" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F106" s="12"/>
-      <c r="G106" s="12"/>
+      <c r="E106" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="10"/>
+      <c r="G106" s="10"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
@@ -5501,21 +5404,21 @@
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
+      <c r="A109" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B109" s="12"/>
-      <c r="C109" s="13" t="s">
+      <c r="B109" s="10"/>
+      <c r="C109" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D109" s="13" t="s">
+      <c r="D109" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E109" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F109" s="12"/>
-      <c r="G109" s="12"/>
+      <c r="E109" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" s="10"/>
+      <c r="G109" s="10"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -5555,21 +5458,21 @@
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="12" t="s">
+      <c r="A112" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B112" s="12"/>
-      <c r="C112" s="13" t="s">
+      <c r="B112" s="10"/>
+      <c r="C112" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D112" s="13" t="s">
+      <c r="D112" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E112" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" s="12"/>
-      <c r="G112" s="12"/>
+      <c r="E112" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="10"/>
+      <c r="G112" s="10"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
@@ -5609,21 +5512,21 @@
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="12" t="s">
+      <c r="A115" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B115" s="12"/>
-      <c r="C115" s="13" t="s">
+      <c r="B115" s="10"/>
+      <c r="C115" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D115" s="13" t="s">
+      <c r="D115" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E115" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F115" s="12"/>
-      <c r="G115" s="12"/>
+      <c r="E115" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F115" s="10"/>
+      <c r="G115" s="10"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
@@ -5663,40 +5566,40 @@
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="B118" s="10"/>
-      <c r="C118" s="11" t="s">
+      <c r="B118" s="8"/>
+      <c r="C118" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D118" s="11" t="s">
+      <c r="D118" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E118" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F118" s="10"/>
-      <c r="G118" s="10" t="s">
+      <c r="E118" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" s="8"/>
+      <c r="G118" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="12" t="s">
+      <c r="A119" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B119" s="12"/>
-      <c r="C119" s="13" t="s">
+      <c r="B119" s="10"/>
+      <c r="C119" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D119" s="13" t="s">
+      <c r="D119" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E119" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F119" s="12"/>
-      <c r="G119" s="12" t="s">
+      <c r="E119" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F119" s="10"/>
+      <c r="G119" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5741,21 +5644,21 @@
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="12" t="s">
+      <c r="A122" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="B122" s="12"/>
-      <c r="C122" s="13" t="s">
+      <c r="B122" s="10"/>
+      <c r="C122" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D122" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E122" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" s="12"/>
-      <c r="G122" s="12" t="s">
+      <c r="E122" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="10"/>
+      <c r="G122" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5800,21 +5703,21 @@
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="12" t="s">
+      <c r="A125" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B125" s="12"/>
-      <c r="C125" s="13" t="s">
+      <c r="B125" s="10"/>
+      <c r="C125" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="D125" s="13" t="s">
+      <c r="D125" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="E125" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125" s="12"/>
-      <c r="G125" s="12" t="s">
+      <c r="E125" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" s="10"/>
+      <c r="G125" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5859,21 +5762,21 @@
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="12" t="s">
+      <c r="A128" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B128" s="12"/>
-      <c r="C128" s="13" t="s">
+      <c r="B128" s="10"/>
+      <c r="C128" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="D128" s="13" t="s">
+      <c r="D128" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="E128" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F128" s="12"/>
-      <c r="G128" s="12" t="s">
+      <c r="E128" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" s="10"/>
+      <c r="G128" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5918,21 +5821,21 @@
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="12" t="s">
+      <c r="A131" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B131" s="12"/>
-      <c r="C131" s="13" t="s">
+      <c r="B131" s="10"/>
+      <c r="C131" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D131" s="13" t="s">
+      <c r="D131" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="E131" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F131" s="12"/>
-      <c r="G131" s="12" t="s">
+      <c r="E131" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="10"/>
+      <c r="G131" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5977,21 +5880,21 @@
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="12" t="s">
+      <c r="A134" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B134" s="12"/>
-      <c r="C134" s="13" t="s">
+      <c r="B134" s="10"/>
+      <c r="C134" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D134" s="13" t="s">
+      <c r="D134" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E134" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F134" s="12"/>
-      <c r="G134" s="12" t="s">
+      <c r="E134" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" s="10"/>
+      <c r="G134" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6036,40 +5939,40 @@
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="10" t="s">
+      <c r="A137" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="B137" s="10"/>
-      <c r="C137" s="11" t="s">
+      <c r="B137" s="8"/>
+      <c r="C137" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D137" s="11" t="s">
+      <c r="D137" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E137" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F137" s="10"/>
-      <c r="G137" s="10" t="s">
+      <c r="E137" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F137" s="8"/>
+      <c r="G137" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="12" t="s">
+      <c r="A138" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B138" s="12"/>
-      <c r="C138" s="13" t="s">
+      <c r="B138" s="10"/>
+      <c r="C138" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D138" s="13" t="s">
+      <c r="D138" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E138" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F138" s="12"/>
-      <c r="G138" s="12" t="s">
+      <c r="E138" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="10"/>
+      <c r="G138" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6134,21 +6037,21 @@
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="12" t="s">
+      <c r="A142" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B142" s="12"/>
-      <c r="C142" s="13" t="s">
+      <c r="B142" s="10"/>
+      <c r="C142" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="D142" s="13" t="s">
+      <c r="D142" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E142" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F142" s="12"/>
-      <c r="G142" s="12" t="s">
+      <c r="E142" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="10"/>
+      <c r="G142" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6193,21 +6096,21 @@
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="12" t="s">
+      <c r="A145" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B145" s="12"/>
-      <c r="C145" s="13" t="s">
+      <c r="B145" s="10"/>
+      <c r="C145" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D145" s="13" t="s">
+      <c r="D145" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E145" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F145" s="12"/>
-      <c r="G145" s="12" t="s">
+      <c r="E145" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F145" s="10"/>
+      <c r="G145" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6232,21 +6135,21 @@
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="12" t="s">
+      <c r="A147" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B147" s="12"/>
-      <c r="C147" s="13" t="s">
+      <c r="B147" s="10"/>
+      <c r="C147" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D147" s="13" t="s">
+      <c r="D147" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E147" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" s="12"/>
-      <c r="G147" s="12" t="s">
+      <c r="E147" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F147" s="10"/>
+      <c r="G147" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6311,21 +6214,21 @@
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="10" t="s">
+      <c r="A151" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="B151" s="10"/>
-      <c r="C151" s="11" t="s">
+      <c r="B151" s="8"/>
+      <c r="C151" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D151" s="11" t="s">
+      <c r="D151" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E151" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F151" s="10"/>
-      <c r="G151" s="10" t="s">
+      <c r="E151" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="8"/>
+      <c r="G151" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6507,23 +6410,23 @@
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="10" t="s">
+      <c r="A161" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B161" s="10"/>
-      <c r="C161" s="11" t="s">
+      <c r="B161" s="8"/>
+      <c r="C161" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D161" s="16">
+      <c r="D161" s="14">
         <v>46153</v>
       </c>
-      <c r="E161" s="11" t="s">
+      <c r="E161" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F161" s="10" t="s">
+      <c r="F161" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G161" s="10" t="s">
+      <c r="G161" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6732,23 +6635,23 @@
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="10" t="s">
+      <c r="A172" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="B172" s="10"/>
-      <c r="C172" s="11" t="s">
+      <c r="B172" s="8"/>
+      <c r="C172" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D172" s="16">
+      <c r="D172" s="14">
         <v>46153</v>
       </c>
-      <c r="E172" s="11" t="s">
+      <c r="E172" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F172" s="10" t="s">
+      <c r="F172" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G172" s="10" t="s">
+      <c r="G172" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6793,23 +6696,23 @@
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="12" t="s">
+      <c r="A175" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="B175" s="12"/>
-      <c r="C175" s="13" t="s">
+      <c r="B175" s="10"/>
+      <c r="C175" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D175" s="17">
+      <c r="D175" s="15">
         <v>46153</v>
       </c>
-      <c r="E175" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F175" s="12" t="s">
+      <c r="E175" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F175" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G175" s="12" t="s">
+      <c r="G175" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6974,23 +6877,23 @@
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="12" t="s">
+      <c r="A184" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="B184" s="12"/>
-      <c r="C184" s="13" t="s">
+      <c r="B184" s="10"/>
+      <c r="C184" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D184" s="17">
+      <c r="D184" s="15">
         <v>46153</v>
       </c>
-      <c r="E184" s="13" t="s">
+      <c r="E184" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F184" s="12" t="s">
+      <c r="F184" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="G184" s="12" t="s">
+      <c r="G184" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7318,21 +7221,21 @@
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A201" s="12" t="s">
+      <c r="A201" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="B201" s="12"/>
-      <c r="C201" s="13" t="s">
+      <c r="B201" s="10"/>
+      <c r="C201" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="D201" s="13" t="s">
+      <c r="D201" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="E201" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F201" s="12"/>
-      <c r="G201" s="12" t="s">
+      <c r="E201" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F201" s="10"/>
+      <c r="G201" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7414,21 +7317,21 @@
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A206" s="12" t="s">
+      <c r="A206" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="B206" s="12"/>
-      <c r="C206" s="13" t="s">
+      <c r="B206" s="10"/>
+      <c r="C206" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="D206" s="13" t="s">
+      <c r="D206" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="E206" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F206" s="12"/>
-      <c r="G206" s="12" t="s">
+      <c r="E206" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F206" s="10"/>
+      <c r="G206" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7530,21 +7433,21 @@
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A212" s="12" t="s">
+      <c r="A212" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B212" s="12"/>
-      <c r="C212" s="13" t="s">
+      <c r="B212" s="10"/>
+      <c r="C212" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D212" s="13" t="s">
+      <c r="D212" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="E212" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F212" s="12"/>
-      <c r="G212" s="12" t="s">
+      <c r="E212" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F212" s="10"/>
+      <c r="G212" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7629,23 +7532,23 @@
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A217" s="10" t="s">
+      <c r="A217" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="B217" s="10"/>
-      <c r="C217" s="11" t="s">
+      <c r="B217" s="8"/>
+      <c r="C217" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="D217" s="16">
+      <c r="D217" s="14">
         <v>46182</v>
       </c>
-      <c r="E217" s="11" t="s">
+      <c r="E217" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="F217" s="10" t="s">
+      <c r="F217" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="G217" s="10" t="s">
+      <c r="G217" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7673,23 +7576,23 @@
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A219" s="10" t="s">
+      <c r="A219" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="B219" s="10"/>
-      <c r="C219" s="11" t="s">
+      <c r="B219" s="8"/>
+      <c r="C219" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="D219" s="16">
+      <c r="D219" s="14">
         <v>46153</v>
       </c>
-      <c r="E219" s="11" t="s">
+      <c r="E219" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F219" s="10" t="s">
+      <c r="F219" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="G219" s="10" t="s">
+      <c r="G219" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7775,61 +7678,61 @@
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A224" s="10" t="s">
+      <c r="A224" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="B224" s="10"/>
-      <c r="C224" s="11" t="s">
+      <c r="B224" s="8"/>
+      <c r="C224" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="D224" s="16">
+      <c r="D224" s="14">
         <v>46227</v>
       </c>
-      <c r="E224" s="11" t="s">
+      <c r="E224" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F224" s="10" t="s">
+      <c r="F224" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="G224" s="10" t="s">
+      <c r="G224" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A225" s="12" t="s">
+      <c r="A225" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="B225" s="12"/>
-      <c r="C225" s="13" t="s">
+      <c r="B225" s="10"/>
+      <c r="C225" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D225" s="13" t="s">
+      <c r="D225" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="E225" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F225" s="12"/>
-      <c r="G225" s="12" t="s">
+      <c r="E225" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F225" s="10"/>
+      <c r="G225" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A226" s="12" t="s">
+      <c r="A226" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="B226" s="12"/>
-      <c r="C226" s="13" t="s">
+      <c r="B226" s="10"/>
+      <c r="C226" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D226" s="13" t="s">
+      <c r="D226" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="E226" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F226" s="12"/>
-      <c r="G226" s="12" t="s">
+      <c r="E226" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F226" s="10"/>
+      <c r="G226" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7874,23 +7777,23 @@
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A229" s="12" t="s">
+      <c r="A229" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="B229" s="12"/>
-      <c r="C229" s="13" t="s">
+      <c r="B229" s="10"/>
+      <c r="C229" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="D229" s="17">
+      <c r="D229" s="15">
         <v>46216</v>
       </c>
-      <c r="E229" s="13" t="s">
+      <c r="E229" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="F229" s="12" t="s">
+      <c r="F229" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="G229" s="12" t="s">
+      <c r="G229" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8018,21 +7921,21 @@
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A236" s="12" t="s">
+      <c r="A236" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="B236" s="12"/>
-      <c r="C236" s="13" t="s">
+      <c r="B236" s="10"/>
+      <c r="C236" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="D236" s="13" t="s">
+      <c r="D236" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="E236" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F236" s="12"/>
-      <c r="G236" s="12" t="s">
+      <c r="E236" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F236" s="10"/>
+      <c r="G236" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8177,21 +8080,21 @@
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A244" s="12" t="s">
+      <c r="A244" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="B244" s="12"/>
-      <c r="C244" s="13" t="s">
+      <c r="B244" s="10"/>
+      <c r="C244" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="D244" s="13" t="s">
+      <c r="D244" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E244" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F244" s="12"/>
-      <c r="G244" s="12" t="s">
+      <c r="E244" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F244" s="10"/>
+      <c r="G244" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8336,21 +8239,21 @@
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A252" s="12" t="s">
+      <c r="A252" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="B252" s="12"/>
-      <c r="C252" s="13" t="s">
+      <c r="B252" s="10"/>
+      <c r="C252" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D252" s="13" t="s">
+      <c r="D252" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E252" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F252" s="12"/>
-      <c r="G252" s="12" t="s">
+      <c r="E252" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F252" s="10"/>
+      <c r="G252" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8375,23 +8278,23 @@
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A254" s="12" t="s">
+      <c r="A254" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="B254" s="12"/>
-      <c r="C254" s="13" t="s">
+      <c r="B254" s="10"/>
+      <c r="C254" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="D254" s="17">
+      <c r="D254" s="15">
         <v>46227</v>
       </c>
-      <c r="E254" s="13" t="s">
+      <c r="E254" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F254" s="12" t="s">
+      <c r="F254" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="G254" s="12" t="s">
+      <c r="G254" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8519,21 +8422,21 @@
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A261" s="12" t="s">
+      <c r="A261" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="B261" s="12"/>
-      <c r="C261" s="13" t="s">
+      <c r="B261" s="10"/>
+      <c r="C261" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="D261" s="13" t="s">
+      <c r="D261" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E261" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F261" s="12"/>
-      <c r="G261" s="12" t="s">
+      <c r="E261" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F261" s="10"/>
+      <c r="G261" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8678,21 +8581,21 @@
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A269" s="12" t="s">
+      <c r="A269" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="B269" s="12"/>
-      <c r="C269" s="13" t="s">
+      <c r="B269" s="10"/>
+      <c r="C269" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D269" s="13" t="s">
+      <c r="D269" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="E269" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F269" s="12"/>
-      <c r="G269" s="12" t="s">
+      <c r="E269" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F269" s="10"/>
+      <c r="G269" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8837,21 +8740,21 @@
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A277" s="12" t="s">
+      <c r="A277" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="B277" s="12"/>
-      <c r="C277" s="13" t="s">
+      <c r="B277" s="10"/>
+      <c r="C277" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D277" s="13" t="s">
+      <c r="D277" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E277" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F277" s="12"/>
-      <c r="G277" s="12" t="s">
+      <c r="E277" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F277" s="10"/>
+      <c r="G277" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8876,21 +8779,21 @@
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A279" s="12" t="s">
+      <c r="A279" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="B279" s="12"/>
-      <c r="C279" s="13" t="s">
+      <c r="B279" s="10"/>
+      <c r="C279" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D279" s="13" t="s">
+      <c r="D279" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E279" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F279" s="12"/>
-      <c r="G279" s="12" t="s">
+      <c r="E279" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F279" s="10"/>
+      <c r="G279" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8995,42 +8898,42 @@
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A285" s="10" t="s">
+      <c r="A285" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="B285" s="10"/>
-      <c r="C285" s="11" t="s">
+      <c r="B285" s="8"/>
+      <c r="C285" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D285" s="16">
+      <c r="D285" s="14">
         <v>46188</v>
       </c>
-      <c r="E285" s="11" t="s">
+      <c r="E285" s="9" t="s">
         <v>514</v>
       </c>
-      <c r="F285" s="10" t="s">
+      <c r="F285" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="G285" s="10" t="s">
+      <c r="G285" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A286" s="12" t="s">
+      <c r="A286" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="B286" s="12"/>
-      <c r="C286" s="13" t="s">
+      <c r="B286" s="10"/>
+      <c r="C286" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D286" s="13" t="s">
+      <c r="D286" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="E286" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F286" s="12"/>
-      <c r="G286" s="12" t="s">
+      <c r="E286" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F286" s="10"/>
+      <c r="G286" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9175,21 +9078,21 @@
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A294" s="12" t="s">
+      <c r="A294" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="B294" s="12"/>
-      <c r="C294" s="13" t="s">
+      <c r="B294" s="10"/>
+      <c r="C294" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="D294" s="13" t="s">
+      <c r="D294" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E294" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F294" s="12"/>
-      <c r="G294" s="12" t="s">
+      <c r="E294" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F294" s="10"/>
+      <c r="G294" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9314,21 +9217,21 @@
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A301" s="12" t="s">
+      <c r="A301" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="B301" s="12"/>
-      <c r="C301" s="13" t="s">
+      <c r="B301" s="10"/>
+      <c r="C301" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="D301" s="13" t="s">
+      <c r="D301" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E301" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F301" s="12"/>
-      <c r="G301" s="12" t="s">
+      <c r="E301" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F301" s="10"/>
+      <c r="G301" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9453,21 +9356,21 @@
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A308" s="12" t="s">
+      <c r="A308" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="B308" s="12"/>
-      <c r="C308" s="13" t="s">
+      <c r="B308" s="10"/>
+      <c r="C308" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="D308" s="13" t="s">
+      <c r="D308" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E308" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F308" s="12"/>
-      <c r="G308" s="12" t="s">
+      <c r="E308" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F308" s="10"/>
+      <c r="G308" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9612,21 +9515,21 @@
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A316" s="12" t="s">
+      <c r="A316" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="B316" s="12"/>
-      <c r="C316" s="13" t="s">
+      <c r="B316" s="10"/>
+      <c r="C316" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D316" s="13" t="s">
+      <c r="D316" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="E316" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F316" s="12"/>
-      <c r="G316" s="12" t="s">
+      <c r="E316" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F316" s="10"/>
+      <c r="G316" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9751,21 +9654,21 @@
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A323" s="12" t="s">
+      <c r="A323" s="10" t="s">
         <v>563</v>
       </c>
-      <c r="B323" s="12"/>
-      <c r="C323" s="13" t="s">
+      <c r="B323" s="10"/>
+      <c r="C323" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D323" s="13" t="s">
+      <c r="D323" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="E323" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F323" s="12"/>
-      <c r="G323" s="12" t="s">
+      <c r="E323" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F323" s="10"/>
+      <c r="G323" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9890,21 +9793,21 @@
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A330" s="12" t="s">
+      <c r="A330" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="B330" s="12"/>
-      <c r="C330" s="13" t="s">
+      <c r="B330" s="10"/>
+      <c r="C330" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="D330" s="13" t="s">
+      <c r="D330" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E330" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F330" s="12"/>
-      <c r="G330" s="12" t="s">
+      <c r="E330" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F330" s="10"/>
+      <c r="G330" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10046,23 +9949,23 @@
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A338" s="12" t="s">
+      <c r="A338" s="10" t="s">
         <v>581</v>
       </c>
-      <c r="B338" s="12"/>
-      <c r="C338" s="13" t="s">
+      <c r="B338" s="10"/>
+      <c r="C338" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="D338" s="17">
+      <c r="D338" s="15">
         <v>46188</v>
       </c>
-      <c r="E338" s="13" t="s">
+      <c r="E338" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="F338" s="12" t="s">
+      <c r="F338" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="G338" s="12" t="s">
+      <c r="G338" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10153,23 +10056,23 @@
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A343" s="12" t="s">
+      <c r="A343" s="10" t="s">
         <v>587</v>
       </c>
-      <c r="B343" s="12"/>
-      <c r="C343" s="13" t="s">
+      <c r="B343" s="10"/>
+      <c r="C343" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D343" s="17">
+      <c r="D343" s="15">
         <v>46154</v>
       </c>
-      <c r="E343" s="13" t="s">
+      <c r="E343" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="F343" s="12" t="s">
+      <c r="F343" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="G343" s="12" t="s">
+      <c r="G343" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10320,21 +10223,21 @@
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A351" s="12" t="s">
+      <c r="A351" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="B351" s="12"/>
-      <c r="C351" s="13" t="s">
+      <c r="B351" s="10"/>
+      <c r="C351" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D351" s="13" t="s">
+      <c r="D351" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="E351" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F351" s="12"/>
-      <c r="G351" s="12" t="s">
+      <c r="E351" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F351" s="10"/>
+      <c r="G351" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10479,21 +10382,21 @@
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A359" s="12" t="s">
+      <c r="A359" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="B359" s="12"/>
-      <c r="C359" s="13" t="s">
+      <c r="B359" s="10"/>
+      <c r="C359" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="D359" s="13" t="s">
+      <c r="D359" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="E359" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F359" s="12"/>
-      <c r="G359" s="12" t="s">
+      <c r="E359" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F359" s="10"/>
+      <c r="G359" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10779,10 +10682,10 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B374" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>212</v>
@@ -10799,10 +10702,10 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B375" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>355</v>
@@ -10818,52 +10721,51 @@
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A376" s="8" t="s">
-        <v>633</v>
-      </c>
-      <c r="B376" s="8"/>
-      <c r="C376" s="9" t="s">
+      <c r="A376" t="s">
+        <v>631</v>
+      </c>
+      <c r="B376" t="s">
+        <v>632</v>
+      </c>
+      <c r="C376" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D376" s="18">
-        <v>46178</v>
-      </c>
-      <c r="E376" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="F376" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="G376" s="8"/>
+      <c r="E376" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G376" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A377" s="10" t="s">
+      <c r="A377" t="s">
         <v>634</v>
       </c>
-      <c r="B377" s="10"/>
-      <c r="C377" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D377" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E377" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F377" s="10"/>
-      <c r="G377" s="10" t="s">
+      <c r="B377" t="s">
+        <v>635</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E377" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G377" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B378" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>16</v>
+        <v>284</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>12</v>
@@ -10873,23 +10775,24 @@
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A379" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="B379" s="10"/>
-      <c r="C379" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D379" s="16">
-        <v>46169</v>
-      </c>
-      <c r="E379" s="11" t="s">
+      <c r="A379" t="s">
         <v>638</v>
       </c>
-      <c r="F379" s="10" t="s">
+      <c r="B379" t="s">
         <v>639</v>
       </c>
-      <c r="G379" s="10"/>
+      <c r="C379" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E379" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G379" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
@@ -10899,47 +10802,47 @@
         <v>641</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>284</v>
+        <v>113</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>642</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G380" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B381" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>284</v>
+        <v>106</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G381" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B382" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D382" s="1" t="s">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>12</v>
@@ -10950,54 +10853,54 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B383" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>113</v>
+        <v>246</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>648</v>
+        <v>308</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G383" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A384" s="12" t="s">
+      <c r="A384" t="s">
         <v>649</v>
       </c>
-      <c r="B384" s="12"/>
-      <c r="C384" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D384" s="13" t="s">
+      <c r="B384" t="s">
+        <v>650</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D384" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="E384" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F384" s="12"/>
-      <c r="G384" s="12"/>
+      <c r="E384" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G384" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B385" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D385" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="E385" s="1" t="s">
         <v>12</v>
       </c>
@@ -11007,30 +10910,33 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B386" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="D386" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="E386" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G386" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B387" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>246</v>
+        <v>657</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>308</v>
@@ -11044,10 +10950,10 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B388" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>253</v>
@@ -11063,33 +10969,34 @@
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A389" s="12" t="s">
-        <v>658</v>
-      </c>
-      <c r="B389" s="12"/>
-      <c r="C389" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D389" s="13" t="s">
-        <v>594</v>
-      </c>
-      <c r="E389" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F389" s="12"/>
-      <c r="G389" s="12" t="s">
-        <v>99</v>
+      <c r="A389" t="s">
+        <v>659</v>
+      </c>
+      <c r="B389" t="s">
+        <v>660</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E389" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G389" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B390" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>106</v>
+        <v>284</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>12</v>
@@ -11100,16 +11007,16 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B391" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>106</v>
+        <v>284</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>206</v>
+        <v>284</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>12</v>
@@ -11120,16 +11027,16 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B392" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>665</v>
+        <v>284</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>308</v>
+        <v>192</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>12</v>
@@ -11140,16 +11047,16 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B393" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>253</v>
+        <v>374</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>594</v>
+        <v>669</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>12</v>
@@ -11159,51 +11066,57 @@
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A394" s="12" t="s">
-        <v>667</v>
-      </c>
-      <c r="B394" s="12"/>
-      <c r="C394" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="D394" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="E394" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F394" s="12"/>
-      <c r="G394" s="12"/>
+      <c r="A394" t="s">
+        <v>670</v>
+      </c>
+      <c r="B394" t="s">
+        <v>671</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="E394" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G394" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="B395" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>192</v>
+        <v>360</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G395" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B396" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>284</v>
+        <v>308</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>12</v>
@@ -11214,16 +11127,16 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B397" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>12</v>
@@ -11234,16 +11147,16 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="B398" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>192</v>
+        <v>289</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>12</v>
@@ -11254,16 +11167,16 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="B399" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>374</v>
+        <v>280</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>678</v>
+        <v>368</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>12</v>
@@ -11274,16 +11187,16 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B400" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>681</v>
+        <v>289</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>12</v>
@@ -11294,16 +11207,16 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B401" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>12</v>
@@ -11314,16 +11227,16 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B402" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>308</v>
+        <v>189</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>444</v>
+        <v>249</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>12</v>
@@ -11334,16 +11247,16 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B403" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>12</v>
@@ -11353,36 +11266,37 @@
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A404" s="12" t="s">
-        <v>688</v>
-      </c>
-      <c r="B404" s="12"/>
-      <c r="C404" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="D404" s="17">
-        <v>46169</v>
-      </c>
-      <c r="E404" s="13" t="s">
-        <v>638</v>
-      </c>
-      <c r="F404" s="12" t="s">
-        <v>639</v>
-      </c>
-      <c r="G404" s="12"/>
+      <c r="A404" t="s">
+        <v>691</v>
+      </c>
+      <c r="B404" t="s">
+        <v>692</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E404" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G404" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B405" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>280</v>
+        <v>189</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>289</v>
+        <v>189</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>12</v>
@@ -11393,59 +11307,65 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B406" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>280</v>
+        <v>204</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>368</v>
+        <v>157</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G406" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B407" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D407" s="1" t="s">
-        <v>289</v>
+        <v>87</v>
+      </c>
+      <c r="D407" s="2">
+        <v>46147</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>12</v>
+        <v>699</v>
+      </c>
+      <c r="F407" t="s">
+        <v>700</v>
       </c>
       <c r="G407" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B408" t="s">
-        <v>696</v>
-      </c>
-      <c r="C408" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D408" s="1" t="s">
-        <v>289</v>
+        <v>702</v>
+      </c>
+      <c r="C408" s="2">
+        <v>46148</v>
+      </c>
+      <c r="D408" s="2">
+        <v>46169</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>12</v>
+        <v>585</v>
+      </c>
+      <c r="F408" t="s">
+        <v>633</v>
       </c>
       <c r="G408" t="s">
         <v>99</v>
@@ -11453,56 +11373,56 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B409" t="s">
-        <v>698</v>
-      </c>
-      <c r="C409" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D409" s="1" t="s">
-        <v>249</v>
+        <v>704</v>
+      </c>
+      <c r="C409" s="2">
+        <v>46148</v>
+      </c>
+      <c r="D409" s="2">
+        <v>46155</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>12</v>
+        <v>588</v>
+      </c>
+      <c r="F409" t="s">
+        <v>700</v>
       </c>
       <c r="G409" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B410" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D410" s="1" t="s">
-        <v>189</v>
+        <v>280</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G410" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="B411" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>189</v>
+        <v>320</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>192</v>
+        <v>320</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>12</v>
@@ -11513,16 +11433,16 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="B412" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>189</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>12</v>
@@ -11533,42 +11453,39 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="B413" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>204</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G413" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B414" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D414" s="2">
-        <v>46147</v>
+        <v>355</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="F414" t="s">
-        <v>710</v>
+        <v>12</v>
       </c>
       <c r="G414" t="s">
         <v>20</v>
@@ -11576,158 +11493,159 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B415" t="s">
-        <v>712</v>
-      </c>
-      <c r="C415" s="2">
-        <v>46148</v>
-      </c>
-      <c r="D415" s="2">
-        <v>46169</v>
+        <v>702</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="F415" t="s">
-        <v>639</v>
+        <v>12</v>
       </c>
       <c r="G415" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B416" t="s">
-        <v>714</v>
-      </c>
-      <c r="C416" s="2">
-        <v>46148</v>
-      </c>
-      <c r="D416" s="2">
-        <v>46155</v>
+        <v>717</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="F416" t="s">
-        <v>710</v>
+        <v>12</v>
       </c>
       <c r="G416" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A417" s="12" t="s">
-        <v>715</v>
-      </c>
-      <c r="B417" s="12"/>
-      <c r="C417" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="D417" s="17">
+      <c r="A417" t="s">
+        <v>718</v>
+      </c>
+      <c r="B417" t="s">
+        <v>719</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D417" s="2">
         <v>46147</v>
       </c>
-      <c r="E417" s="13" t="s">
-        <v>597</v>
-      </c>
-      <c r="F417" s="12" t="s">
-        <v>716</v>
-      </c>
-      <c r="G417" s="12"/>
+      <c r="E417" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F417" t="s">
+        <v>720</v>
+      </c>
+      <c r="G417" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="B418" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>280</v>
+        <v>323</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>725</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G418" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="B419" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>320</v>
+        <v>234</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>320</v>
+        <v>212</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G419" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="B420" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G420" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="B421" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>223</v>
+        <v>328</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G421" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B422" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>355</v>
+        <v>734</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>12</v>
@@ -11738,79 +11656,76 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="B423" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>555</v>
+        <v>295</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>118</v>
+        <v>295</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G423" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="B424" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>485</v>
+        <v>202</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G424" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="B425" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="D425" s="2">
-        <v>46147</v>
+        <v>741</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>741</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F425" t="s">
-        <v>732</v>
+        <v>12</v>
       </c>
       <c r="G425" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="B426" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>323</v>
+        <v>744</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>12</v>
@@ -11821,16 +11736,16 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="B427" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>12</v>
@@ -11841,16 +11756,16 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="B428" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>212</v>
+        <v>355</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>12</v>
@@ -11861,16 +11776,16 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="B429" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>212</v>
+        <v>669</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>328</v>
+        <v>97</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>12</v>
@@ -11881,16 +11796,16 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="B430" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>328</v>
+        <v>253</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>747</v>
+        <v>485</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>12</v>
@@ -11901,16 +11816,16 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="B431" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>295</v>
+        <v>488</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>295</v>
+        <v>490</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>12</v>
@@ -11921,19 +11836,22 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="B432" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D432" s="1" t="s">
-        <v>202</v>
+        <v>490</v>
+      </c>
+      <c r="D432" s="2">
+        <v>46149</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F432" t="s">
+        <v>749</v>
       </c>
       <c r="G432" t="s">
         <v>20</v>
@@ -11941,19 +11859,22 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="B433" t="s">
-        <v>753</v>
-      </c>
-      <c r="C433" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="D433" s="1" t="s">
-        <v>754</v>
+        <v>759</v>
+      </c>
+      <c r="C433" s="2">
+        <v>46150</v>
+      </c>
+      <c r="D433" s="2">
+        <v>46156</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
+      </c>
+      <c r="F433" t="s">
+        <v>749</v>
       </c>
       <c r="G433" t="s">
         <v>20</v>
@@ -11961,19 +11882,22 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="B434" t="s">
-        <v>756</v>
-      </c>
-      <c r="C434" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="D434" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
+      </c>
+      <c r="C434" s="2">
+        <v>46157</v>
+      </c>
+      <c r="D434" s="2">
+        <v>46158</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F434" t="s">
+        <v>749</v>
       </c>
       <c r="G434" t="s">
         <v>20</v>
@@ -11981,19 +11905,22 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="B435" t="s">
-        <v>759</v>
-      </c>
-      <c r="C435" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D435" s="1" t="s">
-        <v>204</v>
+        <v>764</v>
+      </c>
+      <c r="C435" s="2">
+        <v>46158</v>
+      </c>
+      <c r="D435" s="2">
+        <v>46160</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>12</v>
+        <v>765</v>
+      </c>
+      <c r="F435" t="s">
+        <v>749</v>
       </c>
       <c r="G435" t="s">
         <v>20</v>
@@ -12001,60 +11928,68 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="B436" t="s">
-        <v>761</v>
-      </c>
-      <c r="C436" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D436" s="1" t="s">
-        <v>355</v>
+        <v>767</v>
+      </c>
+      <c r="C436" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D436" s="2">
+        <v>46169</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>12</v>
+        <v>588</v>
+      </c>
+      <c r="F436" t="s">
+        <v>722</v>
       </c>
       <c r="G436" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A437" s="14" t="s">
-        <v>762</v>
-      </c>
-      <c r="B437" s="14"/>
-      <c r="C437" s="15" t="s">
-        <v>678</v>
-      </c>
-      <c r="D437" s="22">
-        <v>46158</v>
-      </c>
-      <c r="E437" s="15" t="s">
-        <v>763</v>
-      </c>
-      <c r="F437" s="14" t="s">
-        <v>764</v>
-      </c>
-      <c r="G437" s="14" t="s">
+      <c r="A437" t="s">
+        <v>768</v>
+      </c>
+      <c r="B437" t="s">
+        <v>769</v>
+      </c>
+      <c r="C437" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D437" s="2">
+        <v>46169</v>
+      </c>
+      <c r="E437" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F437" t="s">
+        <v>770</v>
+      </c>
+      <c r="G437" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
+        <v>771</v>
+      </c>
+      <c r="B438" t="s">
+        <v>772</v>
+      </c>
+      <c r="C438" s="2">
+        <v>46169</v>
+      </c>
+      <c r="D438" s="2">
+        <v>46170</v>
+      </c>
+      <c r="E438" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="B438" t="s">
-        <v>766</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="D438" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E438" s="1" t="s">
-        <v>12</v>
+      <c r="F438" t="s">
+        <v>722</v>
       </c>
       <c r="G438" t="s">
         <v>20</v>
@@ -12062,19 +11997,22 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B439" t="s">
-        <v>768</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D439" s="1" t="s">
-        <v>485</v>
+        <v>774</v>
+      </c>
+      <c r="C439" s="2">
+        <v>46170</v>
+      </c>
+      <c r="D439" s="2">
+        <v>46171</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>12</v>
+        <v>765</v>
+      </c>
+      <c r="F439" t="s">
+        <v>722</v>
       </c>
       <c r="G439" t="s">
         <v>20</v>
@@ -12082,19 +12020,22 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B440" t="s">
-        <v>770</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="D440" s="1" t="s">
-        <v>490</v>
+        <v>776</v>
+      </c>
+      <c r="C440" s="2">
+        <v>46171</v>
+      </c>
+      <c r="D440" s="2">
+        <v>46175</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>12</v>
+        <v>699</v>
+      </c>
+      <c r="F440" t="s">
+        <v>722</v>
       </c>
       <c r="G440" t="s">
         <v>20</v>
@@ -12102,22 +12043,19 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="B441" t="s">
-        <v>772</v>
+        <v>724</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="D441" s="2">
-        <v>46149</v>
+        <v>294</v>
+      </c>
+      <c r="D441" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F441" t="s">
-        <v>764</v>
+        <v>12</v>
       </c>
       <c r="G441" t="s">
         <v>20</v>
@@ -12125,22 +12063,19 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="B442" t="s">
-        <v>774</v>
-      </c>
-      <c r="C442" s="2">
-        <v>46150</v>
-      </c>
-      <c r="D442" s="2">
-        <v>46156</v>
+        <v>779</v>
+      </c>
+      <c r="C442" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D442" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F442" t="s">
-        <v>764</v>
+        <v>12</v>
       </c>
       <c r="G442" t="s">
         <v>20</v>
@@ -12148,66 +12083,59 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="B443" t="s">
-        <v>776</v>
-      </c>
-      <c r="C443" s="2">
-        <v>46157</v>
-      </c>
-      <c r="D443" s="2">
-        <v>46158</v>
+        <v>731</v>
+      </c>
+      <c r="C443" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D443" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F443" t="s">
-        <v>764</v>
+        <v>12</v>
       </c>
       <c r="G443" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A444" s="14" t="s">
-        <v>777</v>
-      </c>
-      <c r="B444" s="14"/>
-      <c r="C444" s="22">
-        <v>46158</v>
-      </c>
-      <c r="D444" s="22">
-        <v>46171</v>
-      </c>
-      <c r="E444" s="15" t="s">
-        <v>778</v>
-      </c>
-      <c r="F444" s="14" t="s">
-        <v>734</v>
-      </c>
-      <c r="G444" s="14" t="s">
+      <c r="A444" t="s">
+        <v>781</v>
+      </c>
+      <c r="B444" t="s">
+        <v>729</v>
+      </c>
+      <c r="C444" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D444" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E444" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G444" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B445" t="s">
-        <v>780</v>
-      </c>
-      <c r="C445" s="2">
-        <v>46158</v>
-      </c>
-      <c r="D445" s="2">
-        <v>46160</v>
+        <v>733</v>
+      </c>
+      <c r="C445" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D445" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F445" t="s">
-        <v>764</v>
+        <v>12</v>
       </c>
       <c r="G445" t="s">
         <v>20</v>
@@ -12215,22 +12143,19 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B446" t="s">
-        <v>783</v>
-      </c>
-      <c r="C446" s="2">
-        <v>46160</v>
-      </c>
-      <c r="D446" s="2">
-        <v>46169</v>
+        <v>736</v>
+      </c>
+      <c r="C446" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D446" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="F446" t="s">
-        <v>734</v>
+        <v>12</v>
       </c>
       <c r="G446" t="s">
         <v>20</v>
@@ -12241,19 +12166,16 @@
         <v>784</v>
       </c>
       <c r="B447" t="s">
-        <v>785</v>
-      </c>
-      <c r="C447" s="2">
-        <v>46160</v>
-      </c>
-      <c r="D447" s="2">
-        <v>46169</v>
+        <v>738</v>
+      </c>
+      <c r="C447" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D447" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="F447" t="s">
-        <v>786</v>
+        <v>12</v>
       </c>
       <c r="G447" t="s">
         <v>20</v>
@@ -12261,22 +12183,19 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B448" t="s">
-        <v>788</v>
-      </c>
-      <c r="C448" s="2">
-        <v>46169</v>
-      </c>
-      <c r="D448" s="2">
-        <v>46170</v>
+        <v>740</v>
+      </c>
+      <c r="C448" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D448" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F448" t="s">
-        <v>734</v>
+        <v>12</v>
       </c>
       <c r="G448" t="s">
         <v>20</v>
@@ -12284,127 +12203,122 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B449" t="s">
-        <v>790</v>
-      </c>
-      <c r="C449" s="2">
-        <v>46170</v>
-      </c>
-      <c r="D449" s="2">
-        <v>46171</v>
+        <v>743</v>
+      </c>
+      <c r="C449" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D449" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F449" t="s">
-        <v>734</v>
+        <v>12</v>
       </c>
       <c r="G449" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A450" s="14" t="s">
-        <v>791</v>
-      </c>
-      <c r="B450" s="14"/>
-      <c r="C450" s="22">
-        <v>46171</v>
-      </c>
-      <c r="D450" s="22">
-        <v>46175</v>
-      </c>
-      <c r="E450" s="15" t="s">
-        <v>709</v>
-      </c>
-      <c r="F450" s="14" t="s">
-        <v>734</v>
-      </c>
-      <c r="G450" s="14" t="s">
+      <c r="A450" t="s">
+        <v>787</v>
+      </c>
+      <c r="B450" t="s">
+        <v>746</v>
+      </c>
+      <c r="C450" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D450" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E450" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G450" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B451" t="s">
-        <v>793</v>
-      </c>
-      <c r="C451" s="2">
-        <v>46171</v>
-      </c>
-      <c r="D451" s="2">
-        <v>46175</v>
+        <v>789</v>
+      </c>
+      <c r="C451" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D451" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="F451" t="s">
-        <v>734</v>
+        <v>12</v>
       </c>
       <c r="G451" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A452" s="12" t="s">
-        <v>794</v>
-      </c>
-      <c r="B452" s="12"/>
-      <c r="C452" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="D452" s="17">
-        <v>46167</v>
-      </c>
-      <c r="E452" s="13" t="s">
-        <v>585</v>
-      </c>
-      <c r="F452" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G452" s="12"/>
+      <c r="A452" t="s">
+        <v>790</v>
+      </c>
+      <c r="B452" t="s">
+        <v>791</v>
+      </c>
+      <c r="C452" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D452" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E452" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G452" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A453" s="14" t="s">
-        <v>735</v>
-      </c>
-      <c r="B453" s="14"/>
-      <c r="C453" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="D453" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E453" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F453" s="14"/>
-      <c r="G453" s="14" t="s">
-        <v>20</v>
+      <c r="A453" t="s">
+        <v>792</v>
+      </c>
+      <c r="B453" t="s">
+        <v>793</v>
+      </c>
+      <c r="C453" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D453" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E453" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G453" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
+        <v>794</v>
+      </c>
+      <c r="B454" t="s">
         <v>795</v>
       </c>
-      <c r="B454" t="s">
-        <v>737</v>
-      </c>
       <c r="C454" s="1" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G454" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.25">
@@ -12415,16 +12329,19 @@
         <v>797</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D455" s="1" t="s">
-        <v>210</v>
+        <v>444</v>
+      </c>
+      <c r="D455" s="2">
+        <v>46145</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>12</v>
+        <v>699</v>
+      </c>
+      <c r="F455" t="s">
+        <v>17</v>
       </c>
       <c r="G455" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.25">
@@ -12432,254 +12349,286 @@
         <v>798</v>
       </c>
       <c r="B456" t="s">
-        <v>744</v>
-      </c>
-      <c r="C456" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D456" s="1" t="s">
-        <v>295</v>
+        <v>799</v>
+      </c>
+      <c r="C456" s="2">
+        <v>46146</v>
+      </c>
+      <c r="D456" s="2">
+        <v>46150</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F456" t="s">
+        <v>17</v>
       </c>
       <c r="G456" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B457" t="s">
-        <v>742</v>
-      </c>
-      <c r="C457" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D457" s="1" t="s">
-        <v>212</v>
+        <v>801</v>
+      </c>
+      <c r="C457" s="2">
+        <v>46151</v>
+      </c>
+      <c r="D457" s="2">
+        <v>46152</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F457" t="s">
+        <v>17</v>
       </c>
       <c r="G457" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B458" t="s">
-        <v>746</v>
-      </c>
-      <c r="C458" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D458" s="1" t="s">
-        <v>202</v>
+        <v>764</v>
+      </c>
+      <c r="C458" s="2">
+        <v>46152</v>
+      </c>
+      <c r="D458" s="2">
+        <v>46153</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>12</v>
+        <v>765</v>
+      </c>
+      <c r="F458" t="s">
+        <v>17</v>
       </c>
       <c r="G458" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B459" t="s">
-        <v>749</v>
-      </c>
-      <c r="C459" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D459" s="1" t="s">
-        <v>204</v>
+        <v>767</v>
+      </c>
+      <c r="C459" s="2">
+        <v>46153</v>
+      </c>
+      <c r="D459" s="2">
+        <v>46158</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F459" t="s">
+        <v>17</v>
       </c>
       <c r="G459" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B460" t="s">
-        <v>751</v>
-      </c>
-      <c r="C460" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D460" s="1" t="s">
-        <v>204</v>
+        <v>769</v>
+      </c>
+      <c r="C460" s="2">
+        <v>46153</v>
+      </c>
+      <c r="D460" s="2">
+        <v>46158</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F460" t="s">
+        <v>19</v>
       </c>
       <c r="G460" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B461" t="s">
-        <v>753</v>
-      </c>
-      <c r="C461" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D461" s="1" t="s">
-        <v>355</v>
+        <v>772</v>
+      </c>
+      <c r="C461" s="2">
+        <v>46158</v>
+      </c>
+      <c r="D461" s="2">
+        <v>46159</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>12</v>
+        <v>765</v>
+      </c>
+      <c r="F461" t="s">
+        <v>17</v>
       </c>
       <c r="G461" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B462" t="s">
-        <v>756</v>
-      </c>
-      <c r="C462" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D462" s="1" t="s">
-        <v>207</v>
+        <v>774</v>
+      </c>
+      <c r="C462" s="2">
+        <v>46159</v>
+      </c>
+      <c r="D462" s="2">
+        <v>46160</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>12</v>
+        <v>765</v>
+      </c>
+      <c r="F462" t="s">
+        <v>17</v>
       </c>
       <c r="G462" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B463" t="s">
-        <v>759</v>
-      </c>
-      <c r="C463" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="D463" s="1" t="s">
-        <v>390</v>
+        <v>808</v>
+      </c>
+      <c r="C463" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D463" s="2">
+        <v>46163</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>12</v>
+        <v>699</v>
+      </c>
+      <c r="F463" t="s">
+        <v>17</v>
       </c>
       <c r="G463" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="B464" t="s">
-        <v>807</v>
-      </c>
-      <c r="C464" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="D464" s="1" t="s">
-        <v>113</v>
+        <v>810</v>
+      </c>
+      <c r="C464" s="2">
+        <v>46163</v>
+      </c>
+      <c r="D464" s="2">
+        <v>46164</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>12</v>
+        <v>765</v>
+      </c>
+      <c r="F464" t="s">
+        <v>17</v>
       </c>
       <c r="G464" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A465" s="14" t="s">
-        <v>762</v>
-      </c>
-      <c r="B465" s="14"/>
-      <c r="C465" s="15" t="s">
-        <v>648</v>
-      </c>
-      <c r="D465" s="22">
-        <v>46152</v>
-      </c>
-      <c r="E465" s="15" t="s">
-        <v>808</v>
-      </c>
-      <c r="F465" s="14" t="s">
+      <c r="A465" t="s">
+        <v>811</v>
+      </c>
+      <c r="B465" t="s">
+        <v>767</v>
+      </c>
+      <c r="C465" s="2">
+        <v>46164</v>
+      </c>
+      <c r="D465" s="2">
+        <v>46167</v>
+      </c>
+      <c r="E465" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="F465" t="s">
         <v>17</v>
       </c>
-      <c r="G465" s="14" t="s">
+      <c r="G465" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="B466" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>648</v>
+        <v>390</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>97</v>
+        <v>252</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G466" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B467" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D467" s="1" t="s">
-        <v>87</v>
+        <v>488</v>
+      </c>
+      <c r="D467" s="2">
+        <v>46143</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>12</v>
+        <v>765</v>
+      </c>
+      <c r="F467" t="s">
+        <v>816</v>
       </c>
       <c r="G467" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="B468" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>485</v>
+        <v>216</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>85</v>
+        <v>207</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>12</v>
@@ -12690,22 +12639,19 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="B469" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D469" s="2">
-        <v>46145</v>
+        <v>669</v>
+      </c>
+      <c r="D469" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="F469" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G469" t="s">
         <v>31</v>
@@ -12713,22 +12659,19 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B470" t="s">
-        <v>818</v>
-      </c>
-      <c r="C470" s="2">
-        <v>46146</v>
-      </c>
-      <c r="D470" s="2">
-        <v>46150</v>
+        <v>824</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D470" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F470" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G470" t="s">
         <v>31</v>
@@ -12736,66 +12679,59 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B471" t="s">
-        <v>820</v>
-      </c>
-      <c r="C471" s="2">
-        <v>46151</v>
-      </c>
-      <c r="D471" s="2">
-        <v>46152</v>
+        <v>767</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D471" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F471" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G471" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A472" s="14" t="s">
-        <v>777</v>
-      </c>
-      <c r="B472" s="14"/>
-      <c r="C472" s="22">
-        <v>46152</v>
-      </c>
-      <c r="D472" s="22">
-        <v>46160</v>
-      </c>
-      <c r="E472" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="F472" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G472" s="14" t="s">
+      <c r="A472" t="s">
+        <v>828</v>
+      </c>
+      <c r="B472" t="s">
+        <v>829</v>
+      </c>
+      <c r="C472" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D472" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E472" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G472" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="B473" t="s">
-        <v>780</v>
-      </c>
-      <c r="C473" s="2">
-        <v>46152</v>
-      </c>
-      <c r="D473" s="2">
-        <v>46153</v>
+        <v>831</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D473" s="1" t="s">
+        <v>827</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F473" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G473" t="s">
         <v>31</v>
@@ -12803,22 +12739,19 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="B474" t="s">
-        <v>783</v>
-      </c>
-      <c r="C474" s="2">
-        <v>46153</v>
-      </c>
-      <c r="D474" s="2">
-        <v>46158</v>
+        <v>833</v>
+      </c>
+      <c r="C474" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D474" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F474" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G474" t="s">
         <v>31</v>
@@ -12826,22 +12759,19 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="B475" t="s">
-        <v>785</v>
-      </c>
-      <c r="C475" s="2">
-        <v>46153</v>
-      </c>
-      <c r="D475" s="2">
-        <v>46158</v>
+        <v>838</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="D475" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F475" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G475" t="s">
         <v>31</v>
@@ -12849,22 +12779,19 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="B476" t="s">
-        <v>788</v>
-      </c>
-      <c r="C476" s="2">
-        <v>46158</v>
-      </c>
-      <c r="D476" s="2">
-        <v>46159</v>
+        <v>838</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D476" s="1" t="s">
+        <v>485</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F476" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G476" t="s">
         <v>31</v>
@@ -12872,66 +12799,65 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="B477" t="s">
-        <v>790</v>
-      </c>
-      <c r="C477" s="2">
-        <v>46159</v>
-      </c>
-      <c r="D477" s="2">
-        <v>46160</v>
+        <v>841</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D477" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F477" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G477" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A478" s="14" t="s">
-        <v>791</v>
-      </c>
-      <c r="B478" s="14"/>
-      <c r="C478" s="22">
-        <v>46160</v>
-      </c>
-      <c r="D478" s="22">
-        <v>46167</v>
-      </c>
-      <c r="E478" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="F478" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G478" s="14" t="s">
+      <c r="A478" t="s">
+        <v>842</v>
+      </c>
+      <c r="B478" t="s">
+        <v>841</v>
+      </c>
+      <c r="C478" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D478" s="2">
+        <v>46144</v>
+      </c>
+      <c r="E478" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="F478" t="s">
+        <v>836</v>
+      </c>
+      <c r="G478" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>826</v>
+        <v>844</v>
       </c>
       <c r="B479" t="s">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="C479" s="2">
-        <v>46160</v>
+        <v>46144</v>
       </c>
       <c r="D479" s="2">
-        <v>46163</v>
+        <v>46149</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>709</v>
+        <v>845</v>
       </c>
       <c r="F479" t="s">
-        <v>17</v>
+        <v>836</v>
       </c>
       <c r="G479" t="s">
         <v>31</v>
@@ -12939,22 +12865,22 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>828</v>
+        <v>846</v>
       </c>
       <c r="B480" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="C480" s="2">
-        <v>46163</v>
+        <v>46149</v>
       </c>
       <c r="D480" s="2">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>781</v>
+        <v>18</v>
       </c>
       <c r="F480" t="s">
-        <v>17</v>
+        <v>836</v>
       </c>
       <c r="G480" t="s">
         <v>31</v>
@@ -12962,22 +12888,22 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>830</v>
+        <v>847</v>
       </c>
       <c r="B481" t="s">
-        <v>783</v>
+        <v>848</v>
       </c>
       <c r="C481" s="2">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="D481" s="2">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>709</v>
+        <v>597</v>
       </c>
       <c r="F481" t="s">
-        <v>17</v>
+        <v>836</v>
       </c>
       <c r="G481" t="s">
         <v>31</v>
@@ -12985,97 +12911,108 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>831</v>
+        <v>849</v>
       </c>
       <c r="B482" t="s">
-        <v>832</v>
-      </c>
-      <c r="C482" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="D482" s="1" t="s">
-        <v>252</v>
+        <v>850</v>
+      </c>
+      <c r="C482" s="2">
+        <v>46156</v>
+      </c>
+      <c r="D482" s="2">
+        <v>46164</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>12</v>
+        <v>589</v>
+      </c>
+      <c r="F482" t="s">
+        <v>836</v>
       </c>
       <c r="G482" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>833</v>
+        <v>851</v>
       </c>
       <c r="B483" t="s">
-        <v>834</v>
-      </c>
-      <c r="C483" s="1" t="s">
-        <v>488</v>
+        <v>852</v>
+      </c>
+      <c r="C483" s="2">
+        <v>46164</v>
       </c>
       <c r="D483" s="2">
-        <v>46143</v>
+        <v>46165</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>781</v>
+        <v>19</v>
       </c>
       <c r="F483" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G483" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A484" s="12" t="s">
-        <v>836</v>
-      </c>
-      <c r="B484" s="12"/>
-      <c r="C484" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D484" s="17">
+      <c r="A484" t="s">
+        <v>853</v>
+      </c>
+      <c r="B484" t="s">
+        <v>854</v>
+      </c>
+      <c r="C484" s="2">
+        <v>46165</v>
+      </c>
+      <c r="D484" s="2">
         <v>46172</v>
       </c>
-      <c r="E484" s="13" t="s">
-        <v>837</v>
-      </c>
-      <c r="F484" s="12" t="s">
-        <v>838</v>
-      </c>
-      <c r="G484" s="12"/>
+      <c r="E484" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="F484" t="s">
+        <v>856</v>
+      </c>
+      <c r="G484" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A485" s="14" t="s">
-        <v>839</v>
-      </c>
-      <c r="B485" s="14"/>
-      <c r="C485" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D485" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="E485" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F485" s="14"/>
-      <c r="G485" s="14" t="s">
+      <c r="A485" t="s">
+        <v>859</v>
+      </c>
+      <c r="B485" t="s">
+        <v>729</v>
+      </c>
+      <c r="C485" s="2">
+        <v>46172</v>
+      </c>
+      <c r="D485" s="2">
+        <v>46172</v>
+      </c>
+      <c r="E485" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F485" t="s">
+        <v>858</v>
+      </c>
+      <c r="G485" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>840</v>
+        <v>862</v>
       </c>
       <c r="B486" t="s">
-        <v>841</v>
+        <v>820</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>12</v>
@@ -13086,19 +13023,22 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>842</v>
+        <v>863</v>
       </c>
       <c r="B487" t="s">
-        <v>843</v>
+        <v>864</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="D487" s="1" t="s">
-        <v>390</v>
+        <v>490</v>
+      </c>
+      <c r="D487" s="2">
+        <v>46144</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>12</v>
+        <v>597</v>
+      </c>
+      <c r="F487" t="s">
+        <v>861</v>
       </c>
       <c r="G487" t="s">
         <v>31</v>
@@ -13106,19 +13046,22 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="B488" t="s">
-        <v>845</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="D488" s="1" t="s">
-        <v>252</v>
+        <v>824</v>
+      </c>
+      <c r="C488" s="2">
+        <v>46145</v>
+      </c>
+      <c r="D488" s="2">
+        <v>46145</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>12</v>
+        <v>765</v>
+      </c>
+      <c r="F488" t="s">
+        <v>861</v>
       </c>
       <c r="G488" t="s">
         <v>31</v>
@@ -13126,58 +13069,68 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
       <c r="B489" t="s">
-        <v>783</v>
-      </c>
-      <c r="C489" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D489" s="1" t="s">
-        <v>360</v>
+        <v>767</v>
+      </c>
+      <c r="C489" s="2">
+        <v>46146</v>
+      </c>
+      <c r="D489" s="2">
+        <v>46147</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>12</v>
+        <v>597</v>
+      </c>
+      <c r="F489" t="s">
+        <v>861</v>
       </c>
       <c r="G489" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A490" s="14" t="s">
-        <v>847</v>
-      </c>
-      <c r="B490" s="14"/>
-      <c r="C490" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="D490" s="15" t="s">
-        <v>848</v>
-      </c>
-      <c r="E490" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F490" s="14"/>
-      <c r="G490" s="14" t="s">
+      <c r="A490" t="s">
+        <v>869</v>
+      </c>
+      <c r="B490" t="s">
+        <v>829</v>
+      </c>
+      <c r="C490" s="2">
+        <v>46146</v>
+      </c>
+      <c r="D490" s="2">
+        <v>46146</v>
+      </c>
+      <c r="E490" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F490" t="s">
+        <v>861</v>
+      </c>
+      <c r="G490" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>849</v>
+        <v>870</v>
       </c>
       <c r="B491" t="s">
-        <v>850</v>
-      </c>
-      <c r="C491" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D491" s="1" t="s">
-        <v>441</v>
+        <v>831</v>
+      </c>
+      <c r="C491" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D491" s="2">
+        <v>46154</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>12</v>
+        <v>871</v>
+      </c>
+      <c r="F491" t="s">
+        <v>868</v>
       </c>
       <c r="G491" t="s">
         <v>31</v>
@@ -13185,19 +13138,22 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="B492" t="s">
-        <v>852</v>
-      </c>
-      <c r="C492" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="D492" s="1" t="s">
-        <v>848</v>
+        <v>833</v>
+      </c>
+      <c r="C492" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D492" s="2">
+        <v>46148</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>12</v>
+        <v>597</v>
+      </c>
+      <c r="F492" t="s">
+        <v>860</v>
       </c>
       <c r="G492" t="s">
         <v>31</v>
@@ -13205,60 +13161,68 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="B493" t="s">
-        <v>854</v>
-      </c>
-      <c r="C493" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="D493" s="1" t="s">
-        <v>113</v>
+        <v>838</v>
+      </c>
+      <c r="C493" s="2">
+        <v>46149</v>
+      </c>
+      <c r="D493" s="2">
+        <v>46153</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>12</v>
+        <v>845</v>
+      </c>
+      <c r="F493" t="s">
+        <v>860</v>
       </c>
       <c r="G493" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A494" s="14" t="s">
-        <v>855</v>
-      </c>
-      <c r="B494" s="14"/>
-      <c r="C494" s="15" t="s">
-        <v>856</v>
-      </c>
-      <c r="D494" s="22">
-        <v>46164</v>
-      </c>
-      <c r="E494" s="15" t="s">
-        <v>857</v>
-      </c>
-      <c r="F494" s="14" t="s">
-        <v>858</v>
-      </c>
-      <c r="G494" s="14" t="s">
+      <c r="A494" t="s">
+        <v>874</v>
+      </c>
+      <c r="B494" t="s">
+        <v>841</v>
+      </c>
+      <c r="C494" s="2">
+        <v>46153</v>
+      </c>
+      <c r="D494" s="2">
+        <v>46158</v>
+      </c>
+      <c r="E494" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F494" t="s">
+        <v>860</v>
+      </c>
+      <c r="G494" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
       <c r="B495" t="s">
+        <v>838</v>
+      </c>
+      <c r="C495" s="2">
+        <v>46158</v>
+      </c>
+      <c r="D495" s="2">
+        <v>46163</v>
+      </c>
+      <c r="E495" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="F495" t="s">
         <v>860</v>
-      </c>
-      <c r="C495" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="D495" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E495" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="G495" t="s">
         <v>31</v>
@@ -13266,19 +13230,22 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="B496" t="s">
+        <v>841</v>
+      </c>
+      <c r="C496" s="2">
+        <v>46163</v>
+      </c>
+      <c r="D496" s="2">
+        <v>46168</v>
+      </c>
+      <c r="E496" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F496" t="s">
         <v>860</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D496" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="E496" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="G496" t="s">
         <v>31</v>
@@ -13286,19 +13253,22 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="B497" t="s">
-        <v>863</v>
-      </c>
-      <c r="C497" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D497" s="1" t="s">
-        <v>85</v>
+        <v>838</v>
+      </c>
+      <c r="C497" s="2">
+        <v>46168</v>
+      </c>
+      <c r="D497" s="2">
+        <v>46172</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>12</v>
+        <v>845</v>
+      </c>
+      <c r="F497" t="s">
+        <v>860</v>
       </c>
       <c r="G497" t="s">
         <v>31</v>
@@ -13306,91 +13276,87 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>864</v>
+        <v>878</v>
       </c>
       <c r="B498" t="s">
-        <v>863</v>
-      </c>
-      <c r="C498" s="1" t="s">
-        <v>85</v>
+        <v>841</v>
+      </c>
+      <c r="C498" s="2">
+        <v>46172</v>
       </c>
       <c r="D498" s="2">
-        <v>46144</v>
+        <v>46177</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>865</v>
+        <v>18</v>
       </c>
       <c r="F498" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="G498" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
-        <v>866</v>
-      </c>
-      <c r="B499" t="s">
-        <v>860</v>
-      </c>
-      <c r="C499" s="2">
-        <v>46144</v>
-      </c>
-      <c r="D499" s="2">
-        <v>46149</v>
-      </c>
-      <c r="E499" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="F499" t="s">
-        <v>858</v>
-      </c>
-      <c r="G499" t="s">
+      <c r="A499" s="10" t="s">
+        <v>879</v>
+      </c>
+      <c r="B499" s="10"/>
+      <c r="C499" s="15">
+        <v>46148</v>
+      </c>
+      <c r="D499" s="15">
+        <v>46174</v>
+      </c>
+      <c r="E499" s="11" t="s">
+        <v>880</v>
+      </c>
+      <c r="F499" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="G499" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
-        <v>868</v>
-      </c>
-      <c r="B500" t="s">
-        <v>863</v>
-      </c>
-      <c r="C500" s="2">
-        <v>46149</v>
-      </c>
-      <c r="D500" s="2">
+      <c r="A500" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="B500" s="12"/>
+      <c r="C500" s="19">
+        <v>46148</v>
+      </c>
+      <c r="D500" s="19">
         <v>46154</v>
       </c>
-      <c r="E500" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F500" t="s">
-        <v>858</v>
-      </c>
-      <c r="G500" t="s">
+      <c r="E500" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="F500" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="G500" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="B501" t="s">
-        <v>870</v>
+        <v>820</v>
       </c>
       <c r="C501" s="2">
-        <v>46154</v>
+        <v>46148</v>
       </c>
       <c r="D501" s="2">
-        <v>46156</v>
+        <v>46148</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>597</v>
+        <v>765</v>
       </c>
       <c r="F501" t="s">
-        <v>858</v>
+        <v>720</v>
       </c>
       <c r="G501" t="s">
         <v>31</v>
@@ -13398,193 +13364,202 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="B502" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="C502" s="2">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="D502" s="2">
-        <v>46164</v>
+        <v>46151</v>
       </c>
       <c r="E502" s="1" t="s">
-        <v>589</v>
+        <v>699</v>
       </c>
       <c r="F502" t="s">
-        <v>858</v>
+        <v>720</v>
       </c>
       <c r="G502" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A503" s="14" t="s">
-        <v>873</v>
-      </c>
-      <c r="B503" s="14"/>
-      <c r="C503" s="22">
-        <v>46164</v>
-      </c>
-      <c r="D503" s="22">
-        <v>46172</v>
-      </c>
-      <c r="E503" s="15" t="s">
-        <v>874</v>
-      </c>
-      <c r="F503" s="14" t="s">
-        <v>875</v>
-      </c>
-      <c r="G503" s="14"/>
+      <c r="A503" t="s">
+        <v>884</v>
+      </c>
+      <c r="B503" t="s">
+        <v>824</v>
+      </c>
+      <c r="C503" s="2">
+        <v>46152</v>
+      </c>
+      <c r="D503" s="2">
+        <v>46152</v>
+      </c>
+      <c r="E503" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F503" t="s">
+        <v>720</v>
+      </c>
+      <c r="G503" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
       <c r="B504" t="s">
-        <v>877</v>
+        <v>767</v>
       </c>
       <c r="C504" s="2">
-        <v>46164</v>
+        <v>46153</v>
       </c>
       <c r="D504" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>19</v>
+        <v>597</v>
       </c>
       <c r="F504" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="G504" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
-        <v>878</v>
-      </c>
-      <c r="B505" t="s">
-        <v>879</v>
-      </c>
-      <c r="C505" s="2">
-        <v>46165</v>
-      </c>
-      <c r="D505" s="2">
-        <v>46172</v>
-      </c>
-      <c r="E505" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="F505" t="s">
-        <v>881</v>
-      </c>
-      <c r="G505" t="s">
-        <v>882</v>
+      <c r="A505" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="B505" s="12"/>
+      <c r="C505" s="19">
+        <v>46153</v>
+      </c>
+      <c r="D505" s="19">
+        <v>46162</v>
+      </c>
+      <c r="E505" s="13" t="s">
+        <v>886</v>
+      </c>
+      <c r="F505" s="12" t="s">
+        <v>887</v>
+      </c>
+      <c r="G505" s="12" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A506" s="14" t="s">
-        <v>791</v>
-      </c>
-      <c r="B506" s="14"/>
-      <c r="C506" s="22">
-        <v>46172</v>
-      </c>
-      <c r="D506" s="22">
-        <v>46172</v>
-      </c>
-      <c r="E506" s="15" t="s">
-        <v>781</v>
-      </c>
-      <c r="F506" s="14" t="s">
-        <v>883</v>
-      </c>
-      <c r="G506" s="14" t="s">
+      <c r="A506" t="s">
+        <v>888</v>
+      </c>
+      <c r="B506" t="s">
+        <v>829</v>
+      </c>
+      <c r="C506" s="2">
+        <v>46153</v>
+      </c>
+      <c r="D506" s="2">
+        <v>46154</v>
+      </c>
+      <c r="E506" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="F506" t="s">
+        <v>720</v>
+      </c>
+      <c r="G506" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="B507" t="s">
-        <v>742</v>
+        <v>890</v>
       </c>
       <c r="C507" s="2">
-        <v>46172</v>
+        <v>46155</v>
       </c>
       <c r="D507" s="2">
-        <v>46172</v>
+        <v>46162</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>781</v>
+        <v>871</v>
       </c>
       <c r="F507" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="G507" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A508" s="12" t="s">
-        <v>885</v>
-      </c>
-      <c r="B508" s="12"/>
-      <c r="C508" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D508" s="17">
-        <v>46177</v>
-      </c>
-      <c r="E508" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="F508" s="12" t="s">
-        <v>887</v>
-      </c>
-      <c r="G508" s="12" t="s">
+      <c r="A508" t="s">
+        <v>891</v>
+      </c>
+      <c r="B508" t="s">
+        <v>833</v>
+      </c>
+      <c r="C508" s="2">
+        <v>46155</v>
+      </c>
+      <c r="D508" s="2">
+        <v>46155</v>
+      </c>
+      <c r="E508" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F508" t="s">
+        <v>720</v>
+      </c>
+      <c r="G508" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A509" s="14" t="s">
-        <v>839</v>
-      </c>
-      <c r="B509" s="14"/>
-      <c r="C509" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D509" s="22">
-        <v>46147</v>
-      </c>
-      <c r="E509" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F509" s="14" t="s">
-        <v>888</v>
-      </c>
-      <c r="G509" s="14" t="s">
+      <c r="A509" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="B509" s="12"/>
+      <c r="C509" s="19">
+        <v>46156</v>
+      </c>
+      <c r="D509" s="19">
+        <v>46174</v>
+      </c>
+      <c r="E509" s="13" t="s">
+        <v>817</v>
+      </c>
+      <c r="F509" s="12" t="s">
+        <v>720</v>
+      </c>
+      <c r="G509" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B510" t="s">
-        <v>841</v>
-      </c>
-      <c r="C510" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D510" s="1" t="s">
-        <v>24</v>
+        <v>893</v>
+      </c>
+      <c r="C510" s="2">
+        <v>46156</v>
+      </c>
+      <c r="D510" s="2">
+        <v>46162</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>12</v>
+        <v>588</v>
+      </c>
+      <c r="F510" t="s">
+        <v>720</v>
       </c>
       <c r="G510" t="s">
         <v>31</v>
@@ -13592,22 +13567,22 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B511" t="s">
-        <v>891</v>
-      </c>
-      <c r="C511" s="1" t="s">
-        <v>490</v>
+        <v>895</v>
+      </c>
+      <c r="C511" s="2">
+        <v>46163</v>
       </c>
       <c r="D511" s="2">
-        <v>46144</v>
+        <v>46167</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>597</v>
+        <v>18</v>
       </c>
       <c r="F511" t="s">
-        <v>888</v>
+        <v>720</v>
       </c>
       <c r="G511" t="s">
         <v>31</v>
@@ -13615,89 +13590,85 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B512" t="s">
-        <v>845</v>
+        <v>893</v>
       </c>
       <c r="C512" s="2">
-        <v>46145</v>
+        <v>46168</v>
       </c>
       <c r="D512" s="2">
-        <v>46145</v>
+        <v>46174</v>
       </c>
       <c r="E512" s="1" t="s">
-        <v>781</v>
+        <v>588</v>
       </c>
       <c r="F512" t="s">
-        <v>888</v>
+        <v>720</v>
       </c>
       <c r="G512" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A513" t="s">
-        <v>893</v>
-      </c>
-      <c r="B513" t="s">
-        <v>783</v>
-      </c>
-      <c r="C513" s="2">
-        <v>46146</v>
-      </c>
-      <c r="D513" s="2">
-        <v>46147</v>
-      </c>
-      <c r="E513" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="F513" t="s">
-        <v>888</v>
-      </c>
-      <c r="G513" t="s">
-        <v>31</v>
-      </c>
+      <c r="A513" s="10" t="s">
+        <v>897</v>
+      </c>
+      <c r="B513" s="10"/>
+      <c r="C513" s="15">
+        <v>46156</v>
+      </c>
+      <c r="D513" s="15">
+        <v>46178</v>
+      </c>
+      <c r="E513" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="F513" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="G513" s="10"/>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A514" s="14" t="s">
-        <v>847</v>
-      </c>
-      <c r="B514" s="14"/>
-      <c r="C514" s="22">
-        <v>46146</v>
-      </c>
-      <c r="D514" s="22">
-        <v>46154</v>
-      </c>
-      <c r="E514" s="15" t="s">
-        <v>894</v>
-      </c>
-      <c r="F514" s="14" t="s">
-        <v>895</v>
-      </c>
-      <c r="G514" s="14" t="s">
+      <c r="A514" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="B514" s="12"/>
+      <c r="C514" s="19">
+        <v>46156</v>
+      </c>
+      <c r="D514" s="19">
+        <v>46162</v>
+      </c>
+      <c r="E514" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="F514" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="G514" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B515" t="s">
-        <v>850</v>
+        <v>820</v>
       </c>
       <c r="C515" s="2">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="D515" s="2">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="F515" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="G515" t="s">
         <v>31</v>
@@ -13705,22 +13676,22 @@
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="B516" t="s">
-        <v>852</v>
+        <v>883</v>
       </c>
       <c r="C516" s="2">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="D516" s="2">
-        <v>46154</v>
+        <v>46159</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>898</v>
+        <v>699</v>
       </c>
       <c r="F516" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="G516" t="s">
         <v>31</v>
@@ -13728,89 +13699,89 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
+        <v>902</v>
+      </c>
+      <c r="B517" t="s">
+        <v>824</v>
+      </c>
+      <c r="C517" s="2">
+        <v>46160</v>
+      </c>
+      <c r="D517" s="2">
+        <v>46160</v>
+      </c>
+      <c r="E517" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F517" t="s">
         <v>899</v>
-      </c>
-      <c r="B517" t="s">
-        <v>854</v>
-      </c>
-      <c r="C517" s="2">
-        <v>46147</v>
-      </c>
-      <c r="D517" s="2">
-        <v>46148</v>
-      </c>
-      <c r="E517" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="F517" t="s">
-        <v>887</v>
       </c>
       <c r="G517" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A518" s="14" t="s">
-        <v>855</v>
-      </c>
-      <c r="B518" s="14"/>
-      <c r="C518" s="22">
-        <v>46149</v>
-      </c>
-      <c r="D518" s="22">
-        <v>46177</v>
-      </c>
-      <c r="E518" s="15" t="s">
-        <v>900</v>
-      </c>
-      <c r="F518" s="14" t="s">
-        <v>887</v>
-      </c>
-      <c r="G518" s="14" t="s">
+      <c r="A518" t="s">
+        <v>903</v>
+      </c>
+      <c r="B518" t="s">
+        <v>767</v>
+      </c>
+      <c r="C518" s="2">
+        <v>46161</v>
+      </c>
+      <c r="D518" s="2">
+        <v>46162</v>
+      </c>
+      <c r="E518" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="F518" t="s">
+        <v>899</v>
+      </c>
+      <c r="G518" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A519" t="s">
-        <v>901</v>
-      </c>
-      <c r="B519" t="s">
-        <v>860</v>
-      </c>
-      <c r="C519" s="2">
-        <v>46149</v>
-      </c>
-      <c r="D519" s="2">
-        <v>46153</v>
-      </c>
-      <c r="E519" s="1" t="s">
+      <c r="A519" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="B519" s="12"/>
+      <c r="C519" s="19">
+        <v>46164</v>
+      </c>
+      <c r="D519" s="19">
+        <v>46172</v>
+      </c>
+      <c r="E519" s="13" t="s">
         <v>867</v>
       </c>
-      <c r="F519" t="s">
-        <v>887</v>
-      </c>
-      <c r="G519" t="s">
+      <c r="F519" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="G519" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B520" t="s">
-        <v>863</v>
+        <v>829</v>
       </c>
       <c r="C520" s="2">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="D520" s="2">
-        <v>46158</v>
+        <v>46164</v>
       </c>
       <c r="E520" s="1" t="s">
-        <v>18</v>
+        <v>765</v>
       </c>
       <c r="F520" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="G520" t="s">
         <v>31</v>
@@ -13818,22 +13789,22 @@
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B521" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="C521" s="2">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="D521" s="2">
-        <v>46163</v>
+        <v>46172</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="F521" t="s">
-        <v>887</v>
+        <v>904</v>
       </c>
       <c r="G521" t="s">
         <v>31</v>
@@ -13841,1106 +13812,524 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B522" t="s">
-        <v>863</v>
+        <v>833</v>
       </c>
       <c r="C522" s="2">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="D522" s="2">
-        <v>46168</v>
+        <v>46166</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>18</v>
+        <v>597</v>
       </c>
       <c r="F522" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="G522" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A523" t="s">
-        <v>905</v>
-      </c>
-      <c r="B523" t="s">
-        <v>860</v>
-      </c>
-      <c r="C523" s="2">
+      <c r="A523" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="B523" s="12"/>
+      <c r="C523" s="19">
         <v>46168</v>
       </c>
-      <c r="D523" s="2">
-        <v>46172</v>
-      </c>
-      <c r="E523" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="F523" t="s">
-        <v>887</v>
-      </c>
-      <c r="G523" t="s">
-        <v>31</v>
+      <c r="D523" s="19">
+        <v>46178</v>
+      </c>
+      <c r="E523" s="13" t="s">
+        <v>908</v>
+      </c>
+      <c r="F523" s="12" t="s">
+        <v>909</v>
+      </c>
+      <c r="G523" s="12" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B524" t="s">
-        <v>863</v>
+        <v>838</v>
       </c>
       <c r="C524" s="2">
+        <v>46168</v>
+      </c>
+      <c r="D524" s="2">
         <v>46172</v>
       </c>
-      <c r="D524" s="2">
-        <v>46177</v>
-      </c>
       <c r="E524" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="F524" t="s">
+        <v>909</v>
+      </c>
+      <c r="G524" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>911</v>
+      </c>
+      <c r="B525" t="s">
+        <v>841</v>
+      </c>
+      <c r="C525" s="2">
+        <v>46172</v>
+      </c>
+      <c r="D525" s="2">
+        <v>46178</v>
+      </c>
+      <c r="E525" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F524" t="s">
-        <v>887</v>
-      </c>
-      <c r="G524" t="s">
+      <c r="F525" t="s">
+        <v>909</v>
+      </c>
+      <c r="G525" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>912</v>
+      </c>
+      <c r="B526" t="s">
+        <v>913</v>
+      </c>
+      <c r="C526" s="2">
+        <v>46164</v>
+      </c>
+      <c r="D526" s="2">
+        <v>46167</v>
+      </c>
+      <c r="E526" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="F526" t="s">
+        <v>17</v>
+      </c>
+      <c r="G526" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A525" s="12" t="s">
-        <v>907</v>
-      </c>
-      <c r="B525" s="12"/>
-      <c r="C525" s="17">
-        <v>46148</v>
-      </c>
-      <c r="D525" s="17">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A527" s="10" t="s">
+        <v>914</v>
+      </c>
+      <c r="B527" s="10"/>
+      <c r="C527" s="15">
+        <v>46167</v>
+      </c>
+      <c r="D527" s="15">
         <v>46174</v>
       </c>
-      <c r="E525" s="13" t="s">
-        <v>908</v>
-      </c>
-      <c r="F525" s="12" t="s">
-        <v>732</v>
-      </c>
-      <c r="G525" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A526" s="14" t="s">
-        <v>839</v>
-      </c>
-      <c r="B526" s="14"/>
-      <c r="C526" s="22">
-        <v>46148</v>
-      </c>
-      <c r="D526" s="22">
-        <v>46154</v>
-      </c>
-      <c r="E526" s="15" t="s">
+      <c r="E527" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="F526" s="14" t="s">
-        <v>888</v>
-      </c>
-      <c r="G526" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A527" t="s">
-        <v>909</v>
-      </c>
-      <c r="B527" t="s">
-        <v>841</v>
-      </c>
-      <c r="C527" s="2">
-        <v>46148</v>
-      </c>
-      <c r="D527" s="2">
-        <v>46148</v>
-      </c>
-      <c r="E527" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F527" t="s">
-        <v>732</v>
-      </c>
-      <c r="G527" t="s">
-        <v>31</v>
+      <c r="F527" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="G527" s="10" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A528" t="s">
-        <v>910</v>
-      </c>
-      <c r="B528" t="s">
-        <v>911</v>
-      </c>
-      <c r="C528" s="2">
-        <v>46149</v>
-      </c>
-      <c r="D528" s="2">
-        <v>46151</v>
-      </c>
-      <c r="E528" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="F528" t="s">
-        <v>732</v>
-      </c>
-      <c r="G528" t="s">
-        <v>31</v>
+      <c r="A528" s="12" t="s">
+        <v>916</v>
+      </c>
+      <c r="B528" s="12"/>
+      <c r="C528" s="19">
+        <v>46167</v>
+      </c>
+      <c r="D528" s="19">
+        <v>46174</v>
+      </c>
+      <c r="E528" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="F528" s="12" t="s">
+        <v>915</v>
+      </c>
+      <c r="G528" s="12" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B529" t="s">
-        <v>845</v>
+        <v>918</v>
       </c>
       <c r="C529" s="2">
-        <v>46152</v>
+        <v>46167</v>
       </c>
       <c r="D529" s="2">
-        <v>46152</v>
+        <v>46168</v>
       </c>
       <c r="E529" s="1" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="F529" t="s">
-        <v>732</v>
+        <v>915</v>
       </c>
       <c r="G529" t="s">
-        <v>31</v>
+        <v>857</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="B530" t="s">
-        <v>783</v>
+        <v>920</v>
       </c>
       <c r="C530" s="2">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D530" s="2">
-        <v>46154</v>
+        <v>46169</v>
       </c>
       <c r="E530" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F530" t="s">
+        <v>915</v>
+      </c>
+      <c r="G530" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>921</v>
+      </c>
+      <c r="B531" t="s">
+        <v>922</v>
+      </c>
+      <c r="C531" s="2">
+        <v>46169</v>
+      </c>
+      <c r="D531" s="2">
+        <v>46171</v>
+      </c>
+      <c r="E531" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="F530" t="s">
-        <v>888</v>
-      </c>
-      <c r="G530" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A531" s="14" t="s">
-        <v>847</v>
-      </c>
-      <c r="B531" s="14"/>
-      <c r="C531" s="22">
-        <v>46153</v>
-      </c>
-      <c r="D531" s="22">
-        <v>46162</v>
-      </c>
-      <c r="E531" s="15" t="s">
-        <v>914</v>
-      </c>
-      <c r="F531" s="14" t="s">
+      <c r="F531" t="s">
         <v>915</v>
       </c>
-      <c r="G531" s="14" t="s">
-        <v>31</v>
+      <c r="G531" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="B532" t="s">
-        <v>850</v>
+        <v>924</v>
       </c>
       <c r="C532" s="2">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="D532" s="2">
-        <v>46154</v>
+        <v>46172</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>597</v>
+        <v>765</v>
       </c>
       <c r="F532" t="s">
-        <v>732</v>
+        <v>915</v>
       </c>
       <c r="G532" t="s">
-        <v>31</v>
+        <v>857</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="B533" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="C533" s="2">
-        <v>46155</v>
+        <v>46172</v>
       </c>
       <c r="D533" s="2">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="E533" s="1" t="s">
-        <v>898</v>
+        <v>927</v>
       </c>
       <c r="F533" t="s">
         <v>915</v>
       </c>
       <c r="G533" t="s">
-        <v>31</v>
+        <v>857</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="B534" t="s">
-        <v>854</v>
+        <v>930</v>
       </c>
       <c r="C534" s="2">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="D534" s="2">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="F534" t="s">
-        <v>732</v>
+        <v>928</v>
       </c>
       <c r="G534" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A535" s="14" t="s">
-        <v>855</v>
-      </c>
-      <c r="B535" s="14"/>
-      <c r="C535" s="22">
-        <v>46156</v>
-      </c>
-      <c r="D535" s="22">
-        <v>46174</v>
-      </c>
-      <c r="E535" s="15" t="s">
-        <v>837</v>
-      </c>
-      <c r="F535" s="14" t="s">
-        <v>732</v>
-      </c>
-      <c r="G535" s="14" t="s">
-        <v>31</v>
+      <c r="A535" t="s">
+        <v>931</v>
+      </c>
+      <c r="B535" t="s">
+        <v>932</v>
+      </c>
+      <c r="C535" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D535" s="2">
+        <v>46147</v>
+      </c>
+      <c r="E535" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F535" t="s">
+        <v>928</v>
+      </c>
+      <c r="G535" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>920</v>
+        <v>933</v>
       </c>
       <c r="B536" t="s">
-        <v>921</v>
+        <v>934</v>
       </c>
       <c r="C536" s="2">
-        <v>46156</v>
+        <v>46148</v>
       </c>
       <c r="D536" s="2">
-        <v>46162</v>
+        <v>46148</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>588</v>
+        <v>765</v>
       </c>
       <c r="F536" t="s">
-        <v>732</v>
+        <v>928</v>
       </c>
       <c r="G536" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>922</v>
+        <v>935</v>
       </c>
       <c r="B537" t="s">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="C537" s="2">
-        <v>46163</v>
+        <v>46149</v>
       </c>
       <c r="D537" s="2">
-        <v>46167</v>
+        <v>46149</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>18</v>
+        <v>765</v>
       </c>
       <c r="F537" t="s">
-        <v>732</v>
+        <v>928</v>
       </c>
       <c r="G537" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>924</v>
+        <v>937</v>
       </c>
       <c r="B538" t="s">
-        <v>921</v>
+        <v>938</v>
       </c>
       <c r="C538" s="2">
-        <v>46168</v>
+        <v>46150</v>
       </c>
       <c r="D538" s="2">
-        <v>46174</v>
+        <v>46150</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>588</v>
+        <v>765</v>
       </c>
       <c r="F538" t="s">
-        <v>732</v>
+        <v>928</v>
       </c>
       <c r="G538" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A539" s="12" t="s">
-        <v>925</v>
-      </c>
-      <c r="B539" s="12"/>
-      <c r="C539" s="17">
-        <v>46156</v>
-      </c>
-      <c r="D539" s="17">
-        <v>46178</v>
-      </c>
-      <c r="E539" s="13" t="s">
-        <v>926</v>
-      </c>
-      <c r="F539" s="12" t="s">
-        <v>733</v>
-      </c>
-      <c r="G539" s="12"/>
+      <c r="A539" t="s">
+        <v>939</v>
+      </c>
+      <c r="B539" t="s">
+        <v>940</v>
+      </c>
+      <c r="C539" s="2">
+        <v>46153</v>
+      </c>
+      <c r="D539" s="2">
+        <v>46153</v>
+      </c>
+      <c r="E539" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F539" t="s">
+        <v>928</v>
+      </c>
+      <c r="G539" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A540" s="14" t="s">
-        <v>839</v>
-      </c>
-      <c r="B540" s="14"/>
-      <c r="C540" s="22">
-        <v>46156</v>
-      </c>
-      <c r="D540" s="22">
-        <v>46162</v>
-      </c>
-      <c r="E540" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="F540" s="14" t="s">
-        <v>927</v>
-      </c>
-      <c r="G540" s="14" t="s">
-        <v>31</v>
+      <c r="A540" t="s">
+        <v>941</v>
+      </c>
+      <c r="B540" t="s">
+        <v>942</v>
+      </c>
+      <c r="C540" s="2">
+        <v>46154</v>
+      </c>
+      <c r="D540" s="2">
+        <v>46160</v>
+      </c>
+      <c r="E540" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F540" t="s">
+        <v>928</v>
+      </c>
+      <c r="G540" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
+        <v>943</v>
+      </c>
+      <c r="B541" t="s">
+        <v>944</v>
+      </c>
+      <c r="C541" s="2">
+        <v>46161</v>
+      </c>
+      <c r="D541" s="2">
+        <v>46175</v>
+      </c>
+      <c r="E541" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="F541" t="s">
         <v>928</v>
       </c>
-      <c r="B541" t="s">
-        <v>841</v>
-      </c>
-      <c r="C541" s="2">
-        <v>46156</v>
-      </c>
-      <c r="D541" s="2">
-        <v>46156</v>
-      </c>
-      <c r="E541" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F541" t="s">
-        <v>927</v>
-      </c>
       <c r="G541" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A542" t="s">
-        <v>929</v>
-      </c>
-      <c r="B542" t="s">
-        <v>911</v>
-      </c>
-      <c r="C542" s="2">
-        <v>46157</v>
-      </c>
-      <c r="D542" s="2">
-        <v>46159</v>
-      </c>
-      <c r="E542" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="F542" t="s">
-        <v>927</v>
-      </c>
-      <c r="G542" t="s">
-        <v>31</v>
+      <c r="A542" s="16" t="s">
+        <v>945</v>
+      </c>
+      <c r="B542" s="16"/>
+      <c r="C542" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D542" s="17">
+        <v>46174</v>
+      </c>
+      <c r="E542" s="18" t="s">
+        <v>946</v>
+      </c>
+      <c r="F542" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G542" s="16" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>930</v>
+        <v>947</v>
       </c>
       <c r="B543" t="s">
-        <v>845</v>
-      </c>
-      <c r="C543" s="2">
-        <v>46160</v>
-      </c>
-      <c r="D543" s="2">
-        <v>46160</v>
+        <v>948</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D543" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F543" t="s">
-        <v>927</v>
+        <v>12</v>
       </c>
       <c r="G543" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>931</v>
+        <v>949</v>
       </c>
       <c r="B544" t="s">
-        <v>783</v>
-      </c>
-      <c r="C544" s="2">
-        <v>46161</v>
+        <v>950</v>
+      </c>
+      <c r="C544" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="D544" s="2">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>597</v>
+        <v>946</v>
       </c>
       <c r="F544" t="s">
-        <v>927</v>
+        <v>22</v>
       </c>
       <c r="G544" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A545" s="14" t="s">
-        <v>847</v>
-      </c>
-      <c r="B545" s="14"/>
-      <c r="C545" s="22">
-        <v>46164</v>
-      </c>
-      <c r="D545" s="22">
-        <v>46172</v>
-      </c>
-      <c r="E545" s="15" t="s">
-        <v>894</v>
-      </c>
-      <c r="F545" s="14" t="s">
-        <v>932</v>
-      </c>
-      <c r="G545" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A546" t="s">
-        <v>933</v>
-      </c>
-      <c r="B546" t="s">
-        <v>850</v>
-      </c>
-      <c r="C546" s="2">
-        <v>46164</v>
-      </c>
-      <c r="D546" s="2">
-        <v>46164</v>
-      </c>
-      <c r="E546" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F546" t="s">
-        <v>927</v>
-      </c>
-      <c r="G546" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A547" t="s">
-        <v>934</v>
-      </c>
-      <c r="B547" t="s">
-        <v>918</v>
-      </c>
-      <c r="C547" s="2">
-        <v>46165</v>
-      </c>
-      <c r="D547" s="2">
-        <v>46172</v>
-      </c>
-      <c r="E547" s="1" t="s">
-        <v>898</v>
-      </c>
-      <c r="F547" t="s">
-        <v>932</v>
-      </c>
-      <c r="G547" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A548" t="s">
-        <v>935</v>
-      </c>
-      <c r="B548" t="s">
-        <v>854</v>
-      </c>
-      <c r="C548" s="2">
-        <v>46165</v>
-      </c>
-      <c r="D548" s="2">
-        <v>46166</v>
-      </c>
-      <c r="E548" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="F548" t="s">
-        <v>927</v>
-      </c>
-      <c r="G548" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A549" s="14" t="s">
-        <v>855</v>
-      </c>
-      <c r="B549" s="14"/>
-      <c r="C549" s="22">
-        <v>46168</v>
-      </c>
-      <c r="D549" s="22">
-        <v>46178</v>
-      </c>
-      <c r="E549" s="15" t="s">
-        <v>936</v>
-      </c>
-      <c r="F549" s="14" t="s">
-        <v>937</v>
-      </c>
-      <c r="G549" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A550" t="s">
-        <v>938</v>
-      </c>
-      <c r="B550" t="s">
-        <v>860</v>
-      </c>
-      <c r="C550" s="2">
-        <v>46168</v>
-      </c>
-      <c r="D550" s="2">
-        <v>46172</v>
-      </c>
-      <c r="E550" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="F550" t="s">
-        <v>937</v>
-      </c>
-      <c r="G550" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A551" t="s">
-        <v>939</v>
-      </c>
-      <c r="B551" t="s">
-        <v>863</v>
-      </c>
-      <c r="C551" s="2">
-        <v>46172</v>
-      </c>
-      <c r="D551" s="2">
-        <v>46178</v>
-      </c>
-      <c r="E551" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F551" t="s">
-        <v>937</v>
-      </c>
-      <c r="G551" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A552" t="s">
-        <v>940</v>
-      </c>
-      <c r="B552" t="s">
-        <v>941</v>
-      </c>
-      <c r="C552" s="2">
-        <v>46164</v>
-      </c>
-      <c r="D552" s="2">
-        <v>46167</v>
-      </c>
-      <c r="E552" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="F552" t="s">
-        <v>17</v>
-      </c>
-      <c r="G552" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A553" s="12" t="s">
-        <v>942</v>
-      </c>
-      <c r="B553" s="12"/>
-      <c r="C553" s="17">
-        <v>46167</v>
-      </c>
-      <c r="D553" s="17">
-        <v>46174</v>
-      </c>
-      <c r="E553" s="13" t="s">
-        <v>588</v>
-      </c>
-      <c r="F553" s="12" t="s">
-        <v>943</v>
-      </c>
-      <c r="G553" s="12" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A554" s="14" t="s">
-        <v>944</v>
-      </c>
-      <c r="B554" s="14"/>
-      <c r="C554" s="22">
-        <v>46167</v>
-      </c>
-      <c r="D554" s="22">
-        <v>46174</v>
-      </c>
-      <c r="E554" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="F554" s="14" t="s">
-        <v>943</v>
-      </c>
-      <c r="G554" s="14" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A555" t="s">
-        <v>945</v>
-      </c>
-      <c r="B555" t="s">
-        <v>946</v>
-      </c>
-      <c r="C555" s="2">
-        <v>46167</v>
-      </c>
-      <c r="D555" s="2">
-        <v>46168</v>
-      </c>
-      <c r="E555" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F555" t="s">
-        <v>943</v>
-      </c>
-      <c r="G555" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A556" t="s">
-        <v>947</v>
-      </c>
-      <c r="B556" t="s">
-        <v>948</v>
-      </c>
-      <c r="C556" s="2">
-        <v>46167</v>
-      </c>
-      <c r="D556" s="2">
-        <v>46169</v>
-      </c>
-      <c r="E556" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F556" t="s">
-        <v>943</v>
-      </c>
-      <c r="G556" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A557" t="s">
-        <v>949</v>
-      </c>
-      <c r="B557" t="s">
-        <v>950</v>
-      </c>
-      <c r="C557" s="2">
-        <v>46169</v>
-      </c>
-      <c r="D557" s="2">
-        <v>46171</v>
-      </c>
-      <c r="E557" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="F557" t="s">
-        <v>943</v>
-      </c>
-      <c r="G557" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A558" t="s">
-        <v>951</v>
-      </c>
-      <c r="B558" t="s">
-        <v>952</v>
-      </c>
-      <c r="C558" s="2">
-        <v>46171</v>
-      </c>
-      <c r="D558" s="2">
-        <v>46172</v>
-      </c>
-      <c r="E558" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F558" t="s">
-        <v>943</v>
-      </c>
-      <c r="G558" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A559" t="s">
-        <v>953</v>
-      </c>
-      <c r="B559" t="s">
-        <v>954</v>
-      </c>
-      <c r="C559" s="2">
-        <v>46172</v>
-      </c>
-      <c r="D559" s="2">
-        <v>46174</v>
-      </c>
-      <c r="E559" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="F559" t="s">
-        <v>943</v>
-      </c>
-      <c r="G559" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A560" t="s">
-        <v>957</v>
-      </c>
-      <c r="B560" t="s">
-        <v>958</v>
-      </c>
-      <c r="C560" s="2">
-        <v>46143</v>
-      </c>
-      <c r="D560" s="2">
-        <v>46143</v>
-      </c>
-      <c r="E560" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F560" t="s">
-        <v>956</v>
-      </c>
-      <c r="G560" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A561" t="s">
-        <v>959</v>
-      </c>
-      <c r="B561" t="s">
-        <v>960</v>
-      </c>
-      <c r="C561" s="2">
-        <v>46147</v>
-      </c>
-      <c r="D561" s="2">
-        <v>46147</v>
-      </c>
-      <c r="E561" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F561" t="s">
-        <v>956</v>
-      </c>
-      <c r="G561" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A562" t="s">
-        <v>961</v>
-      </c>
-      <c r="B562" t="s">
-        <v>962</v>
-      </c>
-      <c r="C562" s="2">
-        <v>46148</v>
-      </c>
-      <c r="D562" s="2">
-        <v>46148</v>
-      </c>
-      <c r="E562" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F562" t="s">
-        <v>956</v>
-      </c>
-      <c r="G562" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A563" t="s">
-        <v>963</v>
-      </c>
-      <c r="B563" t="s">
-        <v>964</v>
-      </c>
-      <c r="C563" s="2">
-        <v>46149</v>
-      </c>
-      <c r="D563" s="2">
-        <v>46149</v>
-      </c>
-      <c r="E563" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F563" t="s">
-        <v>956</v>
-      </c>
-      <c r="G563" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A564" t="s">
-        <v>965</v>
-      </c>
-      <c r="B564" t="s">
-        <v>966</v>
-      </c>
-      <c r="C564" s="2">
-        <v>46150</v>
-      </c>
-      <c r="D564" s="2">
-        <v>46150</v>
-      </c>
-      <c r="E564" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F564" t="s">
-        <v>956</v>
-      </c>
-      <c r="G564" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A565" t="s">
-        <v>967</v>
-      </c>
-      <c r="B565" t="s">
-        <v>968</v>
-      </c>
-      <c r="C565" s="2">
-        <v>46153</v>
-      </c>
-      <c r="D565" s="2">
-        <v>46153</v>
-      </c>
-      <c r="E565" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F565" t="s">
-        <v>956</v>
-      </c>
-      <c r="G565" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A566" t="s">
-        <v>969</v>
-      </c>
-      <c r="B566" t="s">
-        <v>970</v>
-      </c>
-      <c r="C566" s="2">
-        <v>46154</v>
-      </c>
-      <c r="D566" s="2">
-        <v>46160</v>
-      </c>
-      <c r="E566" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F566" t="s">
-        <v>956</v>
-      </c>
-      <c r="G566" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A567" t="s">
-        <v>971</v>
-      </c>
-      <c r="B567" t="s">
-        <v>972</v>
-      </c>
-      <c r="C567" s="2">
-        <v>46161</v>
-      </c>
-      <c r="D567" s="2">
-        <v>46175</v>
-      </c>
-      <c r="E567" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="F567" t="s">
-        <v>956</v>
-      </c>
-      <c r="G567" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A568" s="19" t="s">
-        <v>973</v>
-      </c>
-      <c r="B568" s="19"/>
-      <c r="C568" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="D568" s="20">
-        <v>46174</v>
-      </c>
-      <c r="E568" s="21" t="s">
-        <v>974</v>
-      </c>
-      <c r="F568" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G568" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A569" t="s">
-        <v>975</v>
-      </c>
-      <c r="B569" t="s">
-        <v>976</v>
-      </c>
-      <c r="C569" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D569" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E569" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G569" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A570" t="s">
-        <v>977</v>
-      </c>
-      <c r="B570" t="s">
-        <v>978</v>
-      </c>
-      <c r="C570" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D570" s="2">
-        <v>46174</v>
-      </c>
-      <c r="E570" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="F570" t="s">
-        <v>22</v>
-      </c>
-      <c r="G570" t="s">
-        <v>99</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G570" xr:uid="{884A9926-2854-412E-98E6-E3B0E258D9F8}"/>
+  <autoFilter ref="A1:G544" xr:uid="{884A9926-2854-412E-98E6-E3B0E258D9F8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Rossall/CL32-RO-May.xlsx
+++ b/data/Rossall/CL32-RO-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Rossall\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3F5BA9-6C09-48F5-A766-EE4CEACDF94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E39D7E7-34AD-4747-9C93-3B0117044776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{330082E0-B90D-417B-B816-56D44A1F8E8F}"/>
   </bookViews>
@@ -3030,7 +3030,7 @@
     <col min="1" max="1" width="35.5703125" customWidth="1"/>
     <col min="2" max="2" width="71.28515625" customWidth="1"/>
     <col min="3" max="4" width="14.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
     <col min="7" max="7" width="31.5703125" customWidth="1"/>
   </cols>

--- a/data/Rossall/CL32-RO-May.xlsx
+++ b/data/Rossall/CL32-RO-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Rossall\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7C2AAE4-D54B-4AC9-BF20-3ACD88DAEBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F964EB-3474-4B62-A71F-D469CEF2A21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{330082E0-B90D-417B-B816-56D44A1F8E8F}"/>
   </bookViews>
@@ -3667,7 +3667,7 @@
   <dimension ref="A1:G622"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="76.7109375" customWidth="1"/>
     <col min="2" max="2" width="54.85546875" customWidth="1"/>
     <col min="3" max="4" width="14.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
